--- a/templates/PRAP_SourceData_Scenarios_v1.0.xlsx
+++ b/templates/PRAP_SourceData_Scenarios_v1.0.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A186"/>
+  <dimension ref="A1:A208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1315,7 +1315,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   A test bed, not a plan. 17 scenarios across 12 projects and 13 people.</t>
+          <t xml:space="preserve">   A test bed, not a plan. 18 scenarios across 12 projects and 13 people.</t>
         </is>
       </c>
     </row>
@@ -1411,55 +1411,59 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>WHAT EACH PROJECT IS FOR</t>
+          <t>IF YOU ARE AN AI AGENT READING THIS FILE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SCN-001  The baseline: every clinical period, every role staffed, all figures calculated.</t>
+          <t xml:space="preserve">   docs/prap_contract.json is the machine-readable contract: every sheet, column,</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Monthly demand by project. Source data (project) &gt; Periods, to see the standard beside each weight.</t>
+          <t xml:space="preserve">   value list and validation rule, with the severity each one carries. Read it before</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr"/>
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   writing to this workbook - it is what stops a plausible-looking column name being</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SCN-002  A project STATED BY HAND, below what its own standard asks for. Trips V-34 short.</t>
+          <t xml:space="preserve">   silently ignored.</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed. The month is marked on the chart and in Resource by project; click it to open the figures behind it.</t>
-        </is>
-      </c>
+      <c r="A140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr"/>
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   To check a file without a browser:</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SCN-003  The same, stated ABOVE the standard. Trips V-34 over.</t>
+          <t xml:space="preserve">      python tools/verify_source_workbook.py &lt;file.xlsx&gt;     full validation + figures</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed - the two directions are counted separately and never netted off.</t>
+          <t xml:space="preserve">      python tools/prap_io.py validate &lt;file&gt;                .xlsx or .prap.json</t>
         </is>
       </c>
     </row>
@@ -1469,14 +1473,14 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SCN-004  A project figure stated by hand OVER an assignment figure also stated by hand. Trips V-33.</t>
+          <t xml:space="preserve">   Every project note_1 says whether the row is a SCENARIO or portfolio filler, so the</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-004 &gt; Monthly estimation. The stated figure and the one actually given are both shown.</t>
+          <t xml:space="preserve">   interesting rows can be found without reading this sheet.</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1490,35 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SCN-005  An assignment on manual with a month that has NO figure. Trips V-31.</t>
+          <t xml:space="preserve">   The figures are checked by four independent implementations that must agree - the</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-005 &gt; Monthly estimation, and the 'Fill the missing months' button.</t>
+          <t xml:space="preserve">   browser engine, tools/prap_io.py, tools/verify_source_workbook.py and the reference</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr"/>
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   inside tools/test_app.py. If your own arithmetic disagrees with all four, it is</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SCN-006  A project figure for a month with NOBODY assigned. Trips V-32 - it cannot be shared out, so it is not applied.</t>
+          <t xml:space="preserve">   probably yours; REQ-CAL-19 is the rule most often got wrong (a project-month IS its</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Monthly estimation.</t>
+          <t xml:space="preserve">   standard, and the people on it DIVIDE it - they do not each add to it).</t>
         </is>
       </c>
     </row>
@@ -1518,191 +1526,317 @@
       <c r="A153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-007  An 'Others' project: three hand-entered periods, three 'Others' roles, no milestone derivation.</t>
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>WHAT EACH PROJECT IS FOR</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (project) &gt; Periods. The derivation button offers 'Standard periods' here, not 'Auto derivation'.</t>
+          <t xml:space="preserve">   SCN-001  The baseline: every clinical period, every role staffed, all figures calculated.</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr"/>
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Monthly demand by project. Source data (project) &gt; Periods, to see the standard beside each weight.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-008  A role NOBODY holds, whose factor is picked up by another role (REQ-CAL-16).</t>
-        </is>
-      </c>
+      <c r="A157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (project) &gt; Utilisation. Clinical Data Associator is unstaffed; its factor lands on the Lead data manager.</t>
+          <t xml:space="preserve">   SCN-002  A project STATED BY HAND, below what its own standard asks for. Trips V-34 short.</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr"/>
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed. The month is marked on the chart and in Resource by project; click it to open the figures behind it.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-009  One role held by THREE people at once, so each claims a third of what one would.</t>
-        </is>
-      </c>
+      <c r="A160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (person) &gt; Monthly estimation &gt; 'Sharing this role'. The project's month does not move when a sharer is added.</t>
+          <t xml:space="preserve">   SCN-003  The same, stated ABOVE the standard. Trips V-34 over.</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr"/>
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed - the two directions are counted separately and never netted off.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-010  A project with NO assignments at all.</t>
-        </is>
-      </c>
+      <c r="A163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Resource by project - it draws nothing, and says so rather than disappearing.</t>
+          <t xml:space="preserve">   SCN-004  A project figure stated by hand OVER an assignment figure also stated by hand. Trips V-33.</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr"/>
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-004 &gt; Monthly estimation. The stated figure and the one actually given are both shown.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-011  A derived column that DISAGREES with its master row. Trips V-13 - the file is read, then the master value wins.</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report. A milestone here records the wrong project_name; Project is the master and is used.</t>
+          <t xml:space="preserve">   SCN-005  An assignment on manual with a month that has NO figure. Trips V-31.</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr"/>
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-005 &gt; Monthly estimation, and the 'Fill the missing months' button.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-012  A clinical trial with NO product recorded. Trips V-04.</t>
-        </is>
-      </c>
+      <c r="A169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report - a warning, not a refusal: the plan is still costed.</t>
+          <t xml:space="preserve">   SCN-006  A project figure for a month with NOBODY assigned. Trips V-32 - it cannot be shared out, so it is not applied.</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr"/>
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Monthly estimation.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-013  An Inspection BEFORE the final DB lock, which does not open the after-close-out period. Trips V-21, for information.</t>
-        </is>
-      </c>
+      <c r="A172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report, and Overall &gt; Project timeline (SCN-005).</t>
+          <t xml:space="preserve">   SCN-007  An 'Others' project: three hand-entered periods, three 'Others' roles, no milestone derivation.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr"/>
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (project) &gt; Periods. The derivation button offers 'Standard periods' here, not 'Auto derivation'.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-014  A milestone name recorded TWICE on one project. Trips V-20.</t>
-        </is>
-      </c>
+      <c r="A175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Milestones (SCN-009).</t>
+          <t xml:space="preserve">   SCN-008  A role NOBODY holds, whose factor is picked up by another role (REQ-CAL-16).</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr"/>
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (project) &gt; Utilisation. Clinical Data Associator is unstaffed; its factor lands on the Lead data manager.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   PSN-002/3  A capacity BELOW the under-allocation floor, so the person can never clear it however fully they are booked. Trips V-22.</t>
-        </is>
-      </c>
+      <c r="A178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report. 0.50 and 0.00 are both legal capacities - V-35 bounds the column at 0.00 to 1.00 - and both are under the 0.60 floor.</t>
+          <t xml:space="preserve">   SCN-009  One role held by THREE people at once, so each claims a third of what one would.</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr"/>
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (person) &gt; Monthly estimation &gt; 'Sharing this role'. The project's month does not move when a sharer is added.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   PSN-001  A person over the 1.50 FTE ceiling, on four projects at once.</t>
-        </is>
-      </c>
+      <c r="A181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Resource by person, and Source data (person) &gt; Utilisation: the bar is outlined where the month crosses a threshold.</t>
+          <t xml:space="preserve">   SCN-010  A project with NO assignments at all.</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr"/>
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Resource by project - it draws nothing, and says so rather than disappearing.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (several)  A role that carries a factor and that NOBODY holds and nothing covers for. Trips V-29, for information - it is work not being counted.</t>
-        </is>
-      </c>
+      <c r="A184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">   SCN-011  A derived column that DISAGREES with its master row. Trips V-13 - the file is read, then the master value wins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report. A milestone here records the wrong project_name; Project is the master and is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SCN-012  A clinical trial with NO product recorded. Trips V-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report - a warning, not a refusal: the plan is still costed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SCN-013  An Inspection BEFORE the final DB lock, which does not open the after-close-out period. Trips V-21, for information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Overall &gt; Project timeline (SCN-005).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SCN-014  A milestone name recorded TWICE on one project. Trips V-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Milestones (SCN-009).</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PSN-002/3  A capacity BELOW the under-allocation floor, so the person can never clear it however fully they are booked. Trips V-22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report. 0.50 and 0.00 are both legal capacities - V-35 bounds the column at 0.00 to 1.00 - and both are under the 0.60 floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PSN-001  A person over the 1.50 FTE ceiling, on four projects at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Resource by person, and Source data (person) &gt; Utilisation: the bar is outlined where the month crosses a threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   BLK-xxx  A milestone dated AFTER the project's own end, which extends the timeline rather than being dropped. Trips V-14, for information. (Large set only.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Overall &gt; Project timeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (several)  A role that carries a factor and that NOBODY holds and nothing covers for. Trips V-29, for information - it is work not being counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">            Look at: The findings report. Distinct from SCN-008, where the unstaffed role IS covered and so is not reported.</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr"/>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5945,7 +6079,7 @@
       </c>
       <c r="U2" s="7" t="inlineStr">
         <is>
-          <t>Nothing unusual. Read this one first - the others are departures from it.</t>
+          <t>SCENARIO. Nothing unusual - read this one first, the others are departures from it.</t>
         </is>
       </c>
       <c r="V2" s="7" t="n"/>
@@ -6040,7 +6174,7 @@
       </c>
       <c r="U3" s="7" t="inlineStr">
         <is>
-          <t>estimation_type = manual. The MonthlyEstimate figures are deliberately smaller than the standard.</t>
+          <t>SCENARIO. estimation_type = manual, with figures deliberately smaller than the standard - V-34 short.</t>
         </is>
       </c>
       <c r="V3" s="7" t="n"/>
@@ -6135,7 +6269,7 @@
       </c>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>estimation_type = manual, figures above the standard.</t>
+          <t>SCENARIO. estimation_type = manual, figures above the standard - V-34 over.</t>
         </is>
       </c>
       <c r="V4" s="7" t="n"/>
@@ -6230,7 +6364,7 @@
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>Both levels manual. The project figure is the mother figure and the people on it are scaled to it (REQ-CAL-18).</t>
+          <t>SCENARIO. Both levels manual. The project figure is the mother figure and the people on it are scaled to it (REQ-CAL-18) - V-33.</t>
         </is>
       </c>
       <c r="V5" s="7" t="n"/>
@@ -6323,7 +6457,11 @@
           <t>automatic</t>
         </is>
       </c>
-      <c r="U6" s="7" t="n"/>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>SCENARIO. One assignment here is manual with a month left unstated - V-31. Its Inspection is also early - V-21.</t>
+        </is>
+      </c>
       <c r="V6" s="7" t="n"/>
       <c r="W6" s="7" t="n"/>
       <c r="X6" s="7" t="n"/>
@@ -6414,7 +6552,11 @@
           <t>manual</t>
         </is>
       </c>
-      <c r="U7" s="7" t="n"/>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>SCENARIO. Manual figures run the whole project; the staffing stops half way, so the later figures cannot be shared out - V-32.</t>
+        </is>
+      </c>
       <c r="V7" s="7" t="n"/>
       <c r="W7" s="7" t="n"/>
       <c r="X7" s="7" t="n"/>
@@ -6499,7 +6641,7 @@
       </c>
       <c r="U8" s="7" t="inlineStr">
         <is>
-          <t>An 'Others' project has no clinical phase and no product; its periods are entered by hand.</t>
+          <t>SCENARIO. An 'Others' project: no clinical phase, no product, and periods entered by hand.</t>
         </is>
       </c>
       <c r="V8" s="7" t="n"/>
@@ -6594,7 +6736,7 @@
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>No Clinical Data Associator is assigned. RoleFactor.absorbed_by sends that work to the Lead data manager.</t>
+          <t>SCENARIO. No Clinical Data Associator is assigned; RoleFactor.absorbed_by sends that work to the Lead data manager.</t>
         </is>
       </c>
       <c r="V9" s="7" t="n"/>
@@ -6687,7 +6829,11 @@
           <t>automatic</t>
         </is>
       </c>
-      <c r="U10" s="7" t="n"/>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>SCENARIO. Three people hold Clinical Data Associator, so each claims a third of the factor. A milestone is also duplicated - V-20.</t>
+        </is>
+      </c>
       <c r="V10" s="7" t="n"/>
       <c r="W10" s="7" t="n"/>
       <c r="X10" s="7" t="n"/>
@@ -6770,7 +6916,11 @@
           <t>automatic</t>
         </is>
       </c>
-      <c r="U11" s="7" t="n"/>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>SCENARIO. No assignments at all - it draws nothing and says so rather than disappearing from the tables.</t>
+        </is>
+      </c>
       <c r="V11" s="7" t="n"/>
       <c r="W11" s="7" t="n"/>
       <c r="X11" s="7" t="n"/>
@@ -6865,7 +7015,7 @@
       </c>
       <c r="U12" s="7" t="inlineStr">
         <is>
-          <t>One milestone row carries a stale project_name - V-13. total_period_months also says 99; that one is recomputed in silence, because the file's value is never trusted for it.</t>
+          <t>SCENARIO. One milestone row carries a stale project_name - V-13. total_period_months also says 99; that one is recomputed in silence, because the file's value is never trusted for it.</t>
         </is>
       </c>
       <c r="V12" s="7" t="n"/>
@@ -6954,7 +7104,11 @@
           <t>automatic</t>
         </is>
       </c>
-      <c r="U13" s="7" t="n"/>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>SCENARIO. A clinical trial with no product recorded - V-04. A warning, not a refusal: the plan is still costed.</t>
+        </is>
+      </c>
       <c r="V13" s="7" t="n"/>
       <c r="W13" s="7" t="n"/>
       <c r="X13" s="7" t="n"/>

--- a/templates/PRAP_SourceData_Scenarios_v1.0.xlsx
+++ b/templates/PRAP_SourceData_Scenarios_v1.0.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestone" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectPeriod" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PeriodFTEStandard" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RoleFactor" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Person" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PersonPeriodWeight" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyEstimate" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="00_README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Project" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Milestone" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ProjectPeriod" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PeriodFTEStandard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RoleFactor" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Person" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Assignment" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PersonPeriodWeight" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MonthlyEstimate" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Lists" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Config" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A208"/>
+  <dimension ref="A1:A212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Schema version 12. Matches PRAP_Development_Plan_v1.0.xlsx, sheet 04_Data_Model.</t>
+          <t>Schema version 14. Matches PRAP_Development_Plan_v1.0.xlsx, sheet 04_Data_Model.</t>
         </is>
       </c>
     </row>
@@ -742,306 +742,310 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Milestone             one row per milestone. Eight standard names.</t>
+          <t xml:space="preserve">   Milestone             one row per milestone. Eight standard names. milestone_highlight</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ProjectPeriod         the periods each project passes through, with their weights.</t>
+          <t xml:space="preserve">                         is optional: pick a colour and that milestone is marked on the</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PeriodFTEStandard  default weights per project type, clinical phase, WORK SCOPE and</t>
+          <t xml:space="preserve">                         Project timeline, on the Overall tab and on the project's own tab.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">                         period. Clinical trials only.</t>
+          <t xml:space="preserve">   ProjectPeriod         the periods each project passes through, with their weights.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   RoleFactor            the relative burden of each role, per project type, clinical phase,</t>
+          <t xml:space="preserve">                         period_highlight is optional: pick a colour and that period is</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">                         WORK SCOPE and period. Leave clinical_phase empty on the 'Others' rows.</t>
+          <t xml:space="preserve">                         drawn in it on the Project timeline; left empty it is drawn gray.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Person                one row per person.</t>
+          <t xml:space="preserve">   PeriodFTEStandard  default weights per project type, clinical phase, WORK SCOPE and</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Assignment            one row per person + project + role.</t>
+          <t xml:space="preserve">                         period. Clinical trials only.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PersonPeriodWeight    optional windows where a person's weight differs.</t>
+          <t xml:space="preserve">   RoleFactor            the relative burden of each role, per project type, clinical phase,</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Lists                 permitted values for every dropdown.</t>
+          <t xml:space="preserve">                         WORK SCOPE and period. Leave clinical_phase empty on the 'Others' rows.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Config                thresholds and settings.</t>
+          <t xml:space="preserve">   Person                one row per person.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Assignment            one row per person + project + role.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>FREE-TEXT NOTES</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PersonPeriodWeight    optional windows where a person's weight differs.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Every sheet carries at least one free-text column, so anything worth recording has a home:</t>
+          <t xml:space="preserve">   Lists                 permitted values for every dropdown.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Project               note_1 .. note_5</t>
+          <t xml:space="preserve">   Config                thresholds and settings.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Milestone             note_1</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      ProjectPeriod         note_1</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>FREE-TEXT NOTES</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      PeriodFTEStandard  note_1</t>
+          <t xml:space="preserve">   Every sheet carries at least one free-text column, so anything worth recording has a home:</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      RoleFactor            role_note</t>
+          <t xml:space="preserve">      Project               note_1 .. note_5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Person                note_1 .. note_5</t>
+          <t xml:space="preserve">      Milestone             note_1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Assignment            note_1 .. note_3</t>
+          <t xml:space="preserve">      ProjectPeriod         note_1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      PersonPeriodWeight    reason</t>
+          <t xml:space="preserve">      PeriodFTEStandard  note_1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Lists                 note_1</t>
+          <t xml:space="preserve">      RoleFactor            role_note</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Config                note</t>
+          <t xml:space="preserve">      Person                note_1 .. note_5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Nothing in a note column affects the calculation. They are carried through import and export</t>
+          <t xml:space="preserve">      Assignment            note_1 .. note_3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   unchanged, so they survive a round trip.</t>
+          <t xml:space="preserve">      PersonPeriodWeight    reason</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Lists                 note_1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>HOW THE CALCULATION USES THIS</t>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Config                note</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   monthly load = project period weight  x  role factor  x  person weight  x  month coverage</t>
+          <t xml:space="preserve">   Nothing in a note column affects the calculation. They are carried through import and export</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">   unchanged, so they survive a round trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>HOW THE CALCULATION USES THIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   monthly load = project period weight  x  role factor  x  person weight  x  month coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">   The result is FTE, where 1.00 FTE = 160 hours per month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Over-allocated:  a person's monthly total above 1.50 FTE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Under-allocated: below 0.80 FTE for three or more consecutive months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>PERIODS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Clinical trial periods are derived from the milestone dates:</t>
+          <t xml:space="preserve">   Over-allocated:  a person's monthly total above 1.50 FTE.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Before-Start-up      project start, to the day before Start-up</t>
+          <t xml:space="preserve">   Under-allocated: below 0.80 FTE for three or more consecutive months.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Start-up             one month before CTA submission, lasting four months</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Conduct              from the end of Start-up to the day before the next close-out</t>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>PERIODS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Close-out (interim)  three months before the interim DB lock, to that lock</t>
+          <t xml:space="preserve">   Clinical trial periods are derived from the milestone dates:</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Conduct  (again)     from the interim DB lock to the day before Close-out (final)</t>
+          <t xml:space="preserve">      Before-Start-up      project start, to the day before Start-up</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Close-out (final)    three months before the final DB lock, to that lock</t>
+          <t xml:space="preserve">      Start-up             one month before CTA submission, lasting four months</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      After Close-out (final)  the inspection activity that follows the final DB lock</t>
+          <t xml:space="preserve">      Conduct              from the end of Start-up to the day before the next close-out</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Close-out (interim)  three months before the interim DB lock, to that lock</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Where 'Protocol (v1)' is recorded, Before-Start-up ends on it and Start-up begins the day after.</t>
+          <t xml:space="preserve">      Conduct  (again)     from the interim DB lock to the day before Close-out (final)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Where 'First SIV' (or 'FPI') is recorded, Start-up ends on it instead of running a fixed four</t>
+          <t xml:space="preserve">      Close-out (final)    three months before the final DB lock, to that lock</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   months. A recorded milestone always beats the month-offset fallback.</t>
+          <t xml:space="preserve">      After Close-out (final)  the inspection activity that follows the final DB lock</t>
         </is>
       </c>
     </row>
@@ -1051,96 +1055,96 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   'Conduct' therefore appears TWICE where a trial has an interim DB lock. period_seq keeps</t>
+          <t xml:space="preserve">   Where 'Protocol (v1)' is recorded, Before-Start-up ends on it and Start-up begins the day after.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the two apart. A period squeezed to nothing by a tight timeline is simply omitted.</t>
+          <t xml:space="preserve">   Where 'First SIV' (or 'FPI') is recorded, Start-up ends on it instead of running a fixed four</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   months. A recorded milestone always beats the month-offset fallback.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   'Inspection' is the one milestone that may be recorded SEVERAL TIMES for a project. Only</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">   'Conduct' therefore appears TWICE where a trial has an interim DB lock. period_seq keeps</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the two apart. A period squeezed to nothing by a tight timeline is simply omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   'Inspection' is the one milestone that may be recorded SEVERAL TIMES for a project. Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">   inspections dated AFTER the final DB lock open the last period; an earlier one stays a marker.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   'Others' projects have no milestones. Their period dates and weights are both typed in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>WORK SCOPE, AND THE NOTE BESIDE IT</t>
-        </is>
-      </c>
-    </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   work_scope_type is the field the CALCULATION reads: with the project type and the phase</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   it selects the standard weights and the role factors. It is a value list, so it has to be</t>
+          <t xml:space="preserve">   'Others' projects have no milestones. Their period dates and weights are both typed in.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   one of a known set.</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr"/>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>WORK SCOPE, AND THE NOTE BESIDE IT</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   outsourcing_scope_det beside it is FREE TEXT and is read by people only. Write what is</t>
+          <t xml:space="preserve">   work_scope_type is the field the CALCULATION reads: with the project type and the phase</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   actually outsourced and to whom - the detail the category cannot carry. Nothing you write</t>
+          <t xml:space="preserve">   it selects the standard weights and the role factors. It is a value list, so it has to be</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   there changes a single figure.</t>
+          <t xml:space="preserve">   one of a known set.</t>
         </is>
       </c>
     </row>
@@ -1150,21 +1154,21 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   It replaces outsourcing_type, which was a value list and is gone at schema 7. A workbook</t>
+          <t xml:space="preserve">   outsourcing_scope_det beside it is FREE TEXT and is read by people only. Write what is</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   still carrying that column is read: its values are moved across, and the application says</t>
+          <t xml:space="preserve">   actually outsourced and to whom - the detail the category cannot carry. Nothing you write</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   so once.</t>
+          <t xml:space="preserve">   there changes a single figure.</t>
         </is>
       </c>
     </row>
@@ -1172,102 +1176,102 @@
       <c r="A95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>ASSIGNMENT DATES ARE OPTIONAL</t>
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   It replaces outsourcing_type, which was a value list and is gone at schema 7. A workbook</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Leave assign_start_date and assign_end_date BLANK for somebody who is on the project for</t>
+          <t xml:space="preserve">   still carrying that column is read: its values are moved across, and the application says</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the whole of it - which is most people. A blank date means the project's own, so the two</t>
+          <t xml:space="preserve">   so once.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   never fall out of step when the project's dates move.</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr"/>
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>ASSIGNMENT DATES ARE OPTIONAL</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fill them in only for a PARTIAL involvement: somebody who joins late, leaves early, or</t>
+          <t xml:space="preserve">   Leave assign_start_date and assign_end_date BLANK for somebody who is on the project for</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   covers one stretch of a longer study.</t>
+          <t xml:space="preserve">   the whole of it - which is most people. A blank date means the project's own, so the two</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr"/>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   never fall out of step when the project's dates move.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>ADDING A PERMITTED VALUE</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
+          <t xml:space="preserve">   Fill them in only for a PARTIAL involvement: somebody who joins late, leaves early, or</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
+          <t xml:space="preserve">   covers one stretch of a longer study.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
-        </is>
-      </c>
+      <c r="A107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr"/>
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>ADDING A PERMITTED VALUE</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PeriodFTEStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
+          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
+          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
         </is>
       </c>
     </row>
@@ -1275,195 +1279,195 @@
       <c r="A112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
+          <t xml:space="preserve">   PeriodFTEStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
+          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the same thing three times.</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr"/>
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>WHAT THIS FILE IS</t>
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   A test bed, not a plan. 18 scenarios across 12 projects and 13 people.</t>
+          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Every project is ONE scenario and is named after it; the note on each row says what</t>
+          <t xml:space="preserve">   the same thing three times.</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   it is for. Nothing here is random and nothing is filler.</t>
-        </is>
-      </c>
+      <c r="A121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr"/>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THIS FILE IS</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   12 projects | 13 people | 55 assignments | 3 override windows | 143 stated months</t>
+          <t xml:space="preserve">   A test bed, not a plan. 18 scenarios across 12 projects and 13 people.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr"/>
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Every project is ONE scenario and is named after it; the note on each row says what</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>WHAT IT DELIBERATELY DOES NOT DO</t>
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   it is for. Nothing here is random and nothing is filler.</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   It does not carry the ERROR-class problems that make the application reject a row -</t>
-        </is>
-      </c>
+      <c r="A126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   an assignment pointing at a project that does not exist, a role with no factor, a</t>
+          <t xml:space="preserve">   12 projects | 13 people | 55 assignments | 3 override windows | 143 stated months</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   date that ends before it starts. Those need a file that is broken on purpose, and a</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   broken file cannot also be the one you click through to watch the application work.</t>
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>WHAT IT DELIBERATELY DOES NOT DO</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The rules reported here are the ones that leave a usable plan behind.</t>
+          <t xml:space="preserve">   It does not carry the ERROR-class problems that make the application reject a row -</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr"/>
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   an assignment pointing at a project that does not exist, a role with no factor, a</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The weights and role factors are ILLUSTRATIVE. Replace them before drawing any</t>
+          <t xml:space="preserve">   date that ends before it starts. Those need a file that is broken on purpose, and a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   conclusion from the output.</t>
+          <t xml:space="preserve">   broken file cannot also be the one you click through to watch the application work.</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr"/>
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The rules reported here are the ones that leave a usable plan behind.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>IF YOU ARE AN AI AGENT READING THIS FILE</t>
-        </is>
-      </c>
+      <c r="A135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   docs/prap_contract.json is the machine-readable contract: every sheet, column,</t>
+          <t xml:space="preserve">   The weights and role factors are ILLUSTRATIVE. Replace them before drawing any</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   value list and validation rule, with the severity each one carries. Read it before</t>
+          <t xml:space="preserve">   conclusion from the output.</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   writing to this workbook - it is what stops a plausible-looking column name being</t>
-        </is>
-      </c>
+      <c r="A138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   silently ignored.</t>
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>IF YOU ARE AN AI AGENT READING THIS FILE</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr"/>
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   docs/prap_contract.json is the machine-readable contract: every sheet, column,</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   To check a file without a browser:</t>
+          <t xml:space="preserve">   value list and validation rule, with the severity each one carries. Read it before</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      python tools/verify_source_workbook.py &lt;file.xlsx&gt;     full validation + figures</t>
+          <t xml:space="preserve">   writing to this workbook - it is what stops a plausible-looking column name being</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      python tools/prap_io.py validate &lt;file&gt;                .xlsx or .prap.json</t>
+          <t xml:space="preserve">   silently ignored.</t>
         </is>
       </c>
     </row>
@@ -1473,76 +1477,76 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Every project note_1 says whether the row is a SCENARIO or portfolio filler, so the</t>
+          <t xml:space="preserve">   To check a file without a browser:</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   interesting rows can be found without reading this sheet.</t>
+          <t xml:space="preserve">      python tools/verify_source_workbook.py &lt;file.xlsx&gt;     full validation + figures</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr"/>
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      python tools/prap_io.py validate &lt;file&gt;                .xlsx or .prap.json</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   The figures are checked by four independent implementations that must agree - the</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   browser engine, tools/prap_io.py, tools/verify_source_workbook.py and the reference</t>
+          <t xml:space="preserve">   Every project note_1 says whether the row is a SCENARIO or portfolio filler, so the</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   inside tools/test_app.py. If your own arithmetic disagrees with all four, it is</t>
+          <t xml:space="preserve">   interesting rows can be found without reading this sheet.</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   probably yours; REQ-CAL-19 is the rule most often got wrong (a project-month IS its</t>
-        </is>
-      </c>
+      <c r="A151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   standard, and the people on it DIVIDE it - they do not each add to it).</t>
+          <t xml:space="preserve">   The figures are checked by four independent implementations that must agree - the</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr"/>
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   browser engine, tools/prap_io.py, tools/verify_source_workbook.py and the reference</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>WHAT EACH PROJECT IS FOR</t>
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   inside tools/test_app.py. If your own arithmetic disagrees with all four, it is</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SCN-001  The baseline: every clinical period, every role staffed, all figures calculated.</t>
+          <t xml:space="preserve">   probably yours; REQ-CAL-19 is the rule most often got wrong (a project-month IS its</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Monthly demand by project. Source data (project) &gt; Periods, to see the standard beside each weight.</t>
+          <t xml:space="preserve">   standard, and the people on it DIVIDE it - they do not each add to it).</t>
         </is>
       </c>
     </row>
@@ -1550,293 +1554,317 @@
       <c r="A157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-002  A project STATED BY HAND, below what its own standard asks for. Trips V-34 short.</t>
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>WHAT EACH PROJECT IS FOR</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed. The month is marked on the chart and in Resource by project; click it to open the figures behind it.</t>
+          <t xml:space="preserve">   SCN-001  The baseline: every clinical period, every role staffed, all figures calculated.</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr"/>
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Monthly demand by project. Source data (project) &gt; Periods, to see the standard beside each weight.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-003  The same, stated ABOVE the standard. Trips V-34 over.</t>
-        </is>
-      </c>
+      <c r="A161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed - the two directions are counted separately and never netted off.</t>
+          <t xml:space="preserve">   SCN-002  A project STATED BY HAND, below what its own standard asks for. Trips V-34 short.</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr"/>
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed. The month is marked on the chart and in Resource by project; click it to open the figures behind it.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-004  A project figure stated by hand OVER an assignment figure also stated by hand. Trips V-33.</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-004 &gt; Monthly estimation. The stated figure and the one actually given are both shown.</t>
+          <t xml:space="preserve">   SCN-003  The same, stated ABOVE the standard. Trips V-34 over.</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr"/>
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Standard vs staffed - the two directions are counted separately and never netted off.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-005  An assignment on manual with a month that has NO figure. Trips V-31.</t>
-        </is>
-      </c>
+      <c r="A167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-005 &gt; Monthly estimation, and the 'Fill the missing months' button.</t>
+          <t xml:space="preserve">   SCN-004  A project figure stated by hand OVER an assignment figure also stated by hand. Trips V-33.</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr"/>
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-004 &gt; Monthly estimation. The stated figure and the one actually given are both shown.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-006  A project figure for a month with NOBODY assigned. Trips V-32 - it cannot be shared out, so it is not applied.</t>
-        </is>
-      </c>
+      <c r="A170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Monthly estimation.</t>
+          <t xml:space="preserve">   SCN-005  An assignment on manual with a month that has NO figure. Trips V-31.</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr"/>
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (person) &gt; PSN-005 &gt; Monthly estimation, and the 'Fill the missing months' button.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-007  An 'Others' project: three hand-entered periods, three 'Others' roles, no milestone derivation.</t>
-        </is>
-      </c>
+      <c r="A173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (project) &gt; Periods. The derivation button offers 'Standard periods' here, not 'Auto derivation'.</t>
+          <t xml:space="preserve">   SCN-006  A project figure for a month with NOBODY assigned. Trips V-32 - it cannot be shared out, so it is not applied.</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr"/>
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Monthly estimation.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-008  A role NOBODY holds, whose factor is picked up by another role (REQ-CAL-16).</t>
-        </is>
-      </c>
+      <c r="A176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (project) &gt; Utilisation. Clinical Data Associator is unstaffed; its factor lands on the Lead data manager.</t>
+          <t xml:space="preserve">   SCN-007  An 'Others' project: three hand-entered periods, three 'Others' roles, no milestone derivation.</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr"/>
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (project) &gt; Periods. The derivation button offers 'Standard periods' here, not 'Auto derivation'.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-009  One role held by THREE people at once, so each claims a third of what one would.</t>
-        </is>
-      </c>
+      <c r="A179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Source data (person) &gt; Monthly estimation &gt; 'Sharing this role'. The project's month does not move when a sharer is added.</t>
+          <t xml:space="preserve">   SCN-008  A role NOBODY holds, whose factor is picked up by another role (REQ-CAL-16).</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr"/>
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (project) &gt; Utilisation. Clinical Data Associator is unstaffed; its factor lands on the Lead data manager.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-010  A project with NO assignments at all.</t>
-        </is>
-      </c>
+      <c r="A182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Resource by project - it draws nothing, and says so rather than disappearing.</t>
+          <t xml:space="preserve">   SCN-009  One role held by THREE people at once, so each claims a third of what one would.</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr"/>
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Source data (person) &gt; Monthly estimation &gt; 'Sharing this role'. The project's month does not move when a sharer is added.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-011  A derived column that DISAGREES with its master row. Trips V-13 - the file is read, then the master value wins.</t>
-        </is>
-      </c>
+      <c r="A185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report. A milestone here records the wrong project_name; Project is the master and is used.</t>
+          <t xml:space="preserve">   SCN-010  A project with NO assignments at all.</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr"/>
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Resource by project - it draws nothing, and says so rather than disappearing.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-012  A clinical trial with NO product recorded. Trips V-04.</t>
-        </is>
-      </c>
+      <c r="A188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report - a warning, not a refusal: the plan is still costed.</t>
+          <t xml:space="preserve">   SCN-011  A derived column that DISAGREES with its master row. Trips V-13 - the file is read, then the master value wins.</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr"/>
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report. A milestone here records the wrong project_name; Project is the master and is used.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-013  An Inspection BEFORE the final DB lock, which does not open the after-close-out period. Trips V-21, for information.</t>
-        </is>
-      </c>
+      <c r="A191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report, and Overall &gt; Project timeline (SCN-005).</t>
+          <t xml:space="preserve">   SCN-012  A clinical trial with NO product recorded. Trips V-04.</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr"/>
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report - a warning, not a refusal: the plan is still costed.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SCN-014  A milestone name recorded TWICE on one project. Trips V-20.</t>
-        </is>
-      </c>
+      <c r="A194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Milestones (SCN-009).</t>
+          <t xml:space="preserve">   SCN-013  An Inspection BEFORE the final DB lock, which does not open the after-close-out period. Trips V-21, for information.</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr"/>
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Overall &gt; Project timeline (SCN-005).</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   PSN-002/3  A capacity BELOW the under-allocation floor, so the person can never clear it however fully they are booked. Trips V-22.</t>
-        </is>
-      </c>
+      <c r="A197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report. 0.50 and 0.00 are both legal capacities - V-35 bounds the column at 0.00 to 1.00 - and both are under the 0.60 floor.</t>
+          <t xml:space="preserve">   SCN-014  A milestone name recorded TWICE on one project. Trips V-20.</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr"/>
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Source data (project) &gt; Milestones (SCN-009).</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   PSN-001  A person over the 1.50 FTE ceiling, on four projects at once.</t>
-        </is>
-      </c>
+      <c r="A200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: Overall &gt; Resource by person, and Source data (person) &gt; Utilisation: the bar is outlined where the month crosses a threshold.</t>
+          <t xml:space="preserve">   PSN-002/3  A capacity BELOW the under-allocation floor, so the person can never clear it however fully they are booked. Trips V-22.</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr"/>
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report. 0.50 and 0.00 are both legal capacities - V-35 bounds the column at 0.00 to 1.00 - and both are under the 0.60 floor.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   BLK-xxx  A milestone dated AFTER the project's own end, which extends the timeline rather than being dropped. Trips V-14, for information. (Large set only.)</t>
-        </is>
-      </c>
+      <c r="A203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Look at: The findings report, and Overall &gt; Project timeline.</t>
+          <t xml:space="preserve">   PSN-001  A person over the 1.50 FTE ceiling, on four projects at once.</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr"/>
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: Overall &gt; Resource by person, and Source data (person) &gt; Utilisation: the bar is outlined where the month crosses a threshold.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (several)  A role that carries a factor and that NOBODY holds and nothing covers for. Trips V-29, for information - it is work not being counted.</t>
-        </is>
-      </c>
+      <c r="A206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">   BLK-xxx  A milestone dated AFTER the project's own end, which extends the timeline rather than being dropped. Trips V-14, for information. (Large set only.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Look at: The findings report, and Overall &gt; Project timeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (several)  A role that carries a factor and that NOBODY holds and nothing covers for. Trips V-29, for information - it is work not being counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">            Look at: The findings report. Distinct from SCN-008, where the unstaffed role IS covered and so is not reported.</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr"/>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4924,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5420,12 +5448,12 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>milestone_highlight</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Before-Start-up</t>
+          <t>Highlight (Red)</t>
         </is>
       </c>
       <c r="C38" s="9" t="n"/>
@@ -5433,12 +5461,12 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>milestone_highlight</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Start-up</t>
+          <t>Highlight (Yellow)</t>
         </is>
       </c>
       <c r="C39" s="9" t="n"/>
@@ -5446,12 +5474,12 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>milestone_highlight</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Conduct (interim)</t>
+          <t>Highlight (Blue)</t>
         </is>
       </c>
       <c r="C40" s="9" t="n"/>
@@ -5459,12 +5487,12 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>milestone_highlight</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Close-out (interim)</t>
+          <t>Highlight (Green)</t>
         </is>
       </c>
       <c r="C41" s="9" t="n"/>
@@ -5472,12 +5500,12 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>milestone_highlight</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Conduct (final)</t>
+          <t>Highlight (Orange)</t>
         </is>
       </c>
       <c r="C42" s="9" t="n"/>
@@ -5485,12 +5513,12 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Close-out (final)</t>
+          <t>Highlight (Red)</t>
         </is>
       </c>
       <c r="C43" s="9" t="n"/>
@@ -5498,12 +5526,12 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>After Close-out (final)</t>
+          <t>Highlight (Yellow)</t>
         </is>
       </c>
       <c r="C44" s="9" t="n"/>
@@ -5511,12 +5539,12 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Highlight (Blue)</t>
         </is>
       </c>
       <c r="C45" s="9" t="n"/>
@@ -5524,12 +5552,12 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Develop</t>
+          <t>Highlight (Green)</t>
         </is>
       </c>
       <c r="C46" s="9" t="n"/>
@@ -5537,12 +5565,12 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Highlight (Orange)</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -5550,12 +5578,12 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Project oversight</t>
+          <t>Before-Start-up</t>
         </is>
       </c>
       <c r="C48" s="9" t="n"/>
@@ -5563,12 +5591,12 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Lead data manager</t>
+          <t>Start-up</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -5576,12 +5604,12 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Clinical Data Associator</t>
+          <t>Conduct (interim)</t>
         </is>
       </c>
       <c r="C50" s="9" t="n"/>
@@ -5589,12 +5617,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Clinical Database Programmer</t>
+          <t>Close-out (interim)</t>
         </is>
       </c>
       <c r="C51" s="9" t="n"/>
@@ -5602,12 +5630,12 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Conduct (final)</t>
         </is>
       </c>
       <c r="C52" s="9" t="n"/>
@@ -5615,12 +5643,12 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>role_others</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Project lead</t>
+          <t>Close-out (final)</t>
         </is>
       </c>
       <c r="C53" s="9" t="n"/>
@@ -5628,12 +5656,12 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>role_others</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Main staff</t>
+          <t>After Close-out (final)</t>
         </is>
       </c>
       <c r="C54" s="9" t="n"/>
@@ -5641,15 +5669,145 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
+          <t>period_name_others</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>period_name_others</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Develop</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>period_name_others</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Project oversight</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Lead data manager</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Clinical Data Associator</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Clinical Database Programmer</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
           <t>role_others</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Project lead</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>role_others</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Main staff</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>role_others</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Other staff</t>
         </is>
       </c>
-      <c r="C55" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5694,7 +5852,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
@@ -17224,15 +17382,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F400"/>
+  <dimension ref="A1:G400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17258,10 +17417,15 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
+          <t>milestone_highlight</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
           <t>milestone_seq</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>note_1</t>
         </is>
@@ -17282,10 +17446,11 @@
       <c r="D2" s="8" t="n">
         <v>46023</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -17302,10 +17467,11 @@
       <c r="D3" s="8" t="n">
         <v>46054</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -17322,10 +17488,11 @@
       <c r="D4" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -17342,10 +17509,11 @@
       <c r="D5" s="8" t="n">
         <v>46204</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -17362,10 +17530,11 @@
       <c r="D6" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -17382,10 +17551,11 @@
       <c r="D7" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -17402,10 +17572,11 @@
       <c r="D8" s="8" t="n">
         <v>46388</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -17422,10 +17593,11 @@
       <c r="D9" s="8" t="n">
         <v>46600</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -17442,10 +17614,11 @@
       <c r="D10" s="8" t="n">
         <v>46631</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -17462,10 +17635,11 @@
       <c r="D11" s="8" t="n">
         <v>46692</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -17482,10 +17656,11 @@
       <c r="D12" s="8" t="n">
         <v>46023</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -17502,10 +17677,11 @@
       <c r="D13" s="8" t="n">
         <v>46054</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -17522,10 +17698,11 @@
       <c r="D14" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -17542,10 +17719,11 @@
       <c r="D15" s="8" t="n">
         <v>46204</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -17562,10 +17740,11 @@
       <c r="D16" s="8" t="n">
         <v>46266</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -17582,10 +17761,11 @@
       <c r="D17" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -17602,10 +17782,11 @@
       <c r="D18" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -17622,10 +17803,11 @@
       <c r="D19" s="8" t="n">
         <v>46388</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -17642,10 +17824,11 @@
       <c r="D20" s="8" t="n">
         <v>46600</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -17662,10 +17845,11 @@
       <c r="D21" s="8" t="n">
         <v>46631</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -17682,10 +17866,11 @@
       <c r="D22" s="8" t="n">
         <v>46023</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -17702,10 +17887,11 @@
       <c r="D23" s="8" t="n">
         <v>46054</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -17722,10 +17908,11 @@
       <c r="D24" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -17742,10 +17929,11 @@
       <c r="D25" s="8" t="n">
         <v>46204</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -17762,10 +17950,11 @@
       <c r="D26" s="8" t="n">
         <v>46235</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>DELIBERATE: a second FPI, which V-20 reports</t>
         </is>
@@ -17786,10 +17975,11 @@
       <c r="D27" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -17806,10 +17996,11 @@
       <c r="D28" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -17826,10 +18017,11 @@
       <c r="D29" s="8" t="n">
         <v>46388</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -17846,10 +18038,11 @@
       <c r="D30" s="8" t="n">
         <v>46600</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -17866,10 +18059,11 @@
       <c r="D31" s="8" t="n">
         <v>46631</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -17886,10 +18080,11 @@
       <c r="D32" s="8" t="n">
         <v>46692</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -17910,10 +18105,11 @@
       <c r="D33" s="8" t="n">
         <v>46023</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>DELIBERATE: a stale project_name, which V-13 reports before the master value is used.</t>
         </is>
@@ -17934,10 +18130,11 @@
       <c r="D34" s="8" t="n">
         <v>46054</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -17954,10 +18151,11 @@
       <c r="D35" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -17974,10 +18172,11 @@
       <c r="D36" s="8" t="n">
         <v>46204</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -17994,10 +18193,11 @@
       <c r="D37" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -18014,10 +18214,11 @@
       <c r="D38" s="8" t="n">
         <v>46357</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -18034,10 +18235,11 @@
       <c r="D39" s="8" t="n">
         <v>46388</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -18054,10 +18256,11 @@
       <c r="D40" s="8" t="n">
         <v>46600</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -18074,10 +18277,11 @@
       <c r="D41" s="8" t="n">
         <v>46631</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -18094,10 +18298,11 @@
       <c r="D42" s="8" t="n">
         <v>46692</v>
       </c>
-      <c r="E42" s="7" t="n">
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n"/>
@@ -18105,6 +18310,7 @@
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n"/>
@@ -18112,6 +18318,7 @@
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="11" t="n"/>
       <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n"/>
@@ -18119,6 +18326,7 @@
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n"/>
@@ -18126,6 +18334,7 @@
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n"/>
@@ -18133,6 +18342,7 @@
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n"/>
@@ -18140,6 +18350,7 @@
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n"/>
@@ -18147,6 +18358,7 @@
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n"/>
@@ -18154,6 +18366,7 @@
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n"/>
@@ -18161,6 +18374,7 @@
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="11" t="n"/>
+      <c r="G51" s="11" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n"/>
@@ -18168,6 +18382,7 @@
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n"/>
@@ -18175,6 +18390,7 @@
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n"/>
@@ -18182,6 +18398,7 @@
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="11" t="n"/>
       <c r="F54" s="11" t="n"/>
+      <c r="G54" s="11" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n"/>
@@ -18189,6 +18406,7 @@
       <c r="D55" s="11" t="n"/>
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="11" t="n"/>
+      <c r="G55" s="11" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n"/>
@@ -18196,6 +18414,7 @@
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="11" t="n"/>
       <c r="F56" s="11" t="n"/>
+      <c r="G56" s="11" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n"/>
@@ -18203,6 +18422,7 @@
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="11" t="n"/>
       <c r="F57" s="11" t="n"/>
+      <c r="G57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n"/>
@@ -18210,6 +18430,7 @@
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="11" t="n"/>
       <c r="F58" s="11" t="n"/>
+      <c r="G58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n"/>
@@ -18217,6 +18438,7 @@
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="11" t="n"/>
       <c r="F59" s="11" t="n"/>
+      <c r="G59" s="11" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n"/>
@@ -18224,6 +18446,7 @@
       <c r="D60" s="11" t="n"/>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="11" t="n"/>
+      <c r="G60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n"/>
@@ -18231,6 +18454,7 @@
       <c r="D61" s="11" t="n"/>
       <c r="E61" s="11" t="n"/>
       <c r="F61" s="11" t="n"/>
+      <c r="G61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n"/>
@@ -18238,6 +18462,7 @@
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="11" t="n"/>
+      <c r="G62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n"/>
@@ -18245,6 +18470,7 @@
       <c r="D63" s="11" t="n"/>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
+      <c r="G63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n"/>
@@ -18252,6 +18478,7 @@
       <c r="D64" s="11" t="n"/>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
+      <c r="G64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n"/>
@@ -18259,6 +18486,7 @@
       <c r="D65" s="11" t="n"/>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
+      <c r="G65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n"/>
@@ -18266,6 +18494,7 @@
       <c r="D66" s="11" t="n"/>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
+      <c r="G66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n"/>
@@ -18273,6 +18502,7 @@
       <c r="D67" s="11" t="n"/>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="11" t="n"/>
+      <c r="G67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n"/>
@@ -18280,6 +18510,7 @@
       <c r="D68" s="11" t="n"/>
       <c r="E68" s="11" t="n"/>
       <c r="F68" s="11" t="n"/>
+      <c r="G68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n"/>
@@ -18287,6 +18518,7 @@
       <c r="D69" s="11" t="n"/>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
+      <c r="G69" s="11" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n"/>
@@ -18294,6 +18526,7 @@
       <c r="D70" s="11" t="n"/>
       <c r="E70" s="11" t="n"/>
       <c r="F70" s="11" t="n"/>
+      <c r="G70" s="11" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n"/>
@@ -18301,6 +18534,7 @@
       <c r="D71" s="11" t="n"/>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
+      <c r="G71" s="11" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n"/>
@@ -18308,6 +18542,7 @@
       <c r="D72" s="11" t="n"/>
       <c r="E72" s="11" t="n"/>
       <c r="F72" s="11" t="n"/>
+      <c r="G72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n"/>
@@ -18315,6 +18550,7 @@
       <c r="D73" s="11" t="n"/>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
+      <c r="G73" s="11" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n"/>
@@ -18322,6 +18558,7 @@
       <c r="D74" s="11" t="n"/>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
+      <c r="G74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n"/>
@@ -18329,6 +18566,7 @@
       <c r="D75" s="11" t="n"/>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
+      <c r="G75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n"/>
@@ -18336,6 +18574,7 @@
       <c r="D76" s="11" t="n"/>
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
+      <c r="G76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n"/>
@@ -18343,6 +18582,7 @@
       <c r="D77" s="11" t="n"/>
       <c r="E77" s="11" t="n"/>
       <c r="F77" s="11" t="n"/>
+      <c r="G77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n"/>
@@ -18350,6 +18590,7 @@
       <c r="D78" s="11" t="n"/>
       <c r="E78" s="11" t="n"/>
       <c r="F78" s="11" t="n"/>
+      <c r="G78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n"/>
@@ -18357,6 +18598,7 @@
       <c r="D79" s="11" t="n"/>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
+      <c r="G79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n"/>
@@ -18364,6 +18606,7 @@
       <c r="D80" s="11" t="n"/>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
+      <c r="G80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n"/>
@@ -18371,6 +18614,7 @@
       <c r="D81" s="11" t="n"/>
       <c r="E81" s="11" t="n"/>
       <c r="F81" s="11" t="n"/>
+      <c r="G81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n"/>
@@ -18378,6 +18622,7 @@
       <c r="D82" s="11" t="n"/>
       <c r="E82" s="11" t="n"/>
       <c r="F82" s="11" t="n"/>
+      <c r="G82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n"/>
@@ -18385,6 +18630,7 @@
       <c r="D83" s="11" t="n"/>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
+      <c r="G83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n"/>
@@ -18392,6 +18638,7 @@
       <c r="D84" s="11" t="n"/>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="n"/>
@@ -18399,6 +18646,7 @@
       <c r="D85" s="11" t="n"/>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
+      <c r="G85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n"/>
@@ -18406,6 +18654,7 @@
       <c r="D86" s="11" t="n"/>
       <c r="E86" s="11" t="n"/>
       <c r="F86" s="11" t="n"/>
+      <c r="G86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n"/>
@@ -18413,6 +18662,7 @@
       <c r="D87" s="11" t="n"/>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
+      <c r="G87" s="11" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n"/>
@@ -18420,6 +18670,7 @@
       <c r="D88" s="11" t="n"/>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
+      <c r="G88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n"/>
@@ -18427,6 +18678,7 @@
       <c r="D89" s="11" t="n"/>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
+      <c r="G89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n"/>
@@ -18434,6 +18686,7 @@
       <c r="D90" s="11" t="n"/>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
+      <c r="G90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="n"/>
@@ -18441,6 +18694,7 @@
       <c r="D91" s="11" t="n"/>
       <c r="E91" s="11" t="n"/>
       <c r="F91" s="11" t="n"/>
+      <c r="G91" s="11" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="n"/>
@@ -18448,6 +18702,7 @@
       <c r="D92" s="11" t="n"/>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
+      <c r="G92" s="11" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="n"/>
@@ -18455,6 +18710,7 @@
       <c r="D93" s="11" t="n"/>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="11" t="n"/>
+      <c r="G93" s="11" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="n"/>
@@ -18462,6 +18718,7 @@
       <c r="D94" s="11" t="n"/>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
+      <c r="G94" s="11" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="n"/>
@@ -18469,6 +18726,7 @@
       <c r="D95" s="11" t="n"/>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
+      <c r="G95" s="11" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="n"/>
@@ -18476,6 +18734,7 @@
       <c r="D96" s="11" t="n"/>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
+      <c r="G96" s="11" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="n"/>
@@ -18483,6 +18742,7 @@
       <c r="D97" s="11" t="n"/>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
+      <c r="G97" s="11" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n"/>
@@ -18490,6 +18750,7 @@
       <c r="D98" s="11" t="n"/>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
+      <c r="G98" s="11" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="n"/>
@@ -18497,6 +18758,7 @@
       <c r="D99" s="11" t="n"/>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
+      <c r="G99" s="11" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="n"/>
@@ -18504,6 +18766,7 @@
       <c r="D100" s="11" t="n"/>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
+      <c r="G100" s="11" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="n"/>
@@ -18511,6 +18774,7 @@
       <c r="D101" s="11" t="n"/>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
+      <c r="G101" s="11" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="n"/>
@@ -18518,6 +18782,7 @@
       <c r="D102" s="11" t="n"/>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
+      <c r="G102" s="11" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="n"/>
@@ -18525,6 +18790,7 @@
       <c r="D103" s="11" t="n"/>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
+      <c r="G103" s="11" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="n"/>
@@ -18532,6 +18798,7 @@
       <c r="D104" s="11" t="n"/>
       <c r="E104" s="11" t="n"/>
       <c r="F104" s="11" t="n"/>
+      <c r="G104" s="11" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="n"/>
@@ -18539,6 +18806,7 @@
       <c r="D105" s="11" t="n"/>
       <c r="E105" s="11" t="n"/>
       <c r="F105" s="11" t="n"/>
+      <c r="G105" s="11" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="n"/>
@@ -18546,6 +18814,7 @@
       <c r="D106" s="11" t="n"/>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
+      <c r="G106" s="11" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="n"/>
@@ -18553,6 +18822,7 @@
       <c r="D107" s="11" t="n"/>
       <c r="E107" s="11" t="n"/>
       <c r="F107" s="11" t="n"/>
+      <c r="G107" s="11" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="n"/>
@@ -18560,6 +18830,7 @@
       <c r="D108" s="11" t="n"/>
       <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
+      <c r="G108" s="11" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="n"/>
@@ -18567,6 +18838,7 @@
       <c r="D109" s="11" t="n"/>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
+      <c r="G109" s="11" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="n"/>
@@ -18574,6 +18846,7 @@
       <c r="D110" s="11" t="n"/>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
+      <c r="G110" s="11" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="n"/>
@@ -18581,6 +18854,7 @@
       <c r="D111" s="11" t="n"/>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
+      <c r="G111" s="11" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="n"/>
@@ -18588,6 +18862,7 @@
       <c r="D112" s="11" t="n"/>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
+      <c r="G112" s="11" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="n"/>
@@ -18595,6 +18870,7 @@
       <c r="D113" s="11" t="n"/>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
+      <c r="G113" s="11" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="n"/>
@@ -18602,6 +18878,7 @@
       <c r="D114" s="11" t="n"/>
       <c r="E114" s="11" t="n"/>
       <c r="F114" s="11" t="n"/>
+      <c r="G114" s="11" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="n"/>
@@ -18609,6 +18886,7 @@
       <c r="D115" s="11" t="n"/>
       <c r="E115" s="11" t="n"/>
       <c r="F115" s="11" t="n"/>
+      <c r="G115" s="11" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="n"/>
@@ -18616,6 +18894,7 @@
       <c r="D116" s="11" t="n"/>
       <c r="E116" s="11" t="n"/>
       <c r="F116" s="11" t="n"/>
+      <c r="G116" s="11" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="n"/>
@@ -18623,6 +18902,7 @@
       <c r="D117" s="11" t="n"/>
       <c r="E117" s="11" t="n"/>
       <c r="F117" s="11" t="n"/>
+      <c r="G117" s="11" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="n"/>
@@ -18630,6 +18910,7 @@
       <c r="D118" s="11" t="n"/>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
+      <c r="G118" s="11" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="n"/>
@@ -18637,6 +18918,7 @@
       <c r="D119" s="11" t="n"/>
       <c r="E119" s="11" t="n"/>
       <c r="F119" s="11" t="n"/>
+      <c r="G119" s="11" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="n"/>
@@ -18644,6 +18926,7 @@
       <c r="D120" s="11" t="n"/>
       <c r="E120" s="11" t="n"/>
       <c r="F120" s="11" t="n"/>
+      <c r="G120" s="11" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="n"/>
@@ -18651,6 +18934,7 @@
       <c r="D121" s="11" t="n"/>
       <c r="E121" s="11" t="n"/>
       <c r="F121" s="11" t="n"/>
+      <c r="G121" s="11" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="n"/>
@@ -18658,6 +18942,7 @@
       <c r="D122" s="11" t="n"/>
       <c r="E122" s="11" t="n"/>
       <c r="F122" s="11" t="n"/>
+      <c r="G122" s="11" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="n"/>
@@ -18665,6 +18950,7 @@
       <c r="D123" s="11" t="n"/>
       <c r="E123" s="11" t="n"/>
       <c r="F123" s="11" t="n"/>
+      <c r="G123" s="11" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="n"/>
@@ -18672,6 +18958,7 @@
       <c r="D124" s="11" t="n"/>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
+      <c r="G124" s="11" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="n"/>
@@ -18679,6 +18966,7 @@
       <c r="D125" s="11" t="n"/>
       <c r="E125" s="11" t="n"/>
       <c r="F125" s="11" t="n"/>
+      <c r="G125" s="11" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="n"/>
@@ -18686,6 +18974,7 @@
       <c r="D126" s="11" t="n"/>
       <c r="E126" s="11" t="n"/>
       <c r="F126" s="11" t="n"/>
+      <c r="G126" s="11" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="n"/>
@@ -18693,6 +18982,7 @@
       <c r="D127" s="11" t="n"/>
       <c r="E127" s="11" t="n"/>
       <c r="F127" s="11" t="n"/>
+      <c r="G127" s="11" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="n"/>
@@ -18700,6 +18990,7 @@
       <c r="D128" s="11" t="n"/>
       <c r="E128" s="11" t="n"/>
       <c r="F128" s="11" t="n"/>
+      <c r="G128" s="11" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="n"/>
@@ -18707,6 +18998,7 @@
       <c r="D129" s="11" t="n"/>
       <c r="E129" s="11" t="n"/>
       <c r="F129" s="11" t="n"/>
+      <c r="G129" s="11" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="n"/>
@@ -18714,6 +19006,7 @@
       <c r="D130" s="11" t="n"/>
       <c r="E130" s="11" t="n"/>
       <c r="F130" s="11" t="n"/>
+      <c r="G130" s="11" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="n"/>
@@ -18721,6 +19014,7 @@
       <c r="D131" s="11" t="n"/>
       <c r="E131" s="11" t="n"/>
       <c r="F131" s="11" t="n"/>
+      <c r="G131" s="11" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="n"/>
@@ -18728,6 +19022,7 @@
       <c r="D132" s="11" t="n"/>
       <c r="E132" s="11" t="n"/>
       <c r="F132" s="11" t="n"/>
+      <c r="G132" s="11" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="n"/>
@@ -18735,6 +19030,7 @@
       <c r="D133" s="11" t="n"/>
       <c r="E133" s="11" t="n"/>
       <c r="F133" s="11" t="n"/>
+      <c r="G133" s="11" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="n"/>
@@ -18742,6 +19038,7 @@
       <c r="D134" s="11" t="n"/>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
+      <c r="G134" s="11" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="n"/>
@@ -18749,6 +19046,7 @@
       <c r="D135" s="11" t="n"/>
       <c r="E135" s="11" t="n"/>
       <c r="F135" s="11" t="n"/>
+      <c r="G135" s="11" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="n"/>
@@ -18756,6 +19054,7 @@
       <c r="D136" s="11" t="n"/>
       <c r="E136" s="11" t="n"/>
       <c r="F136" s="11" t="n"/>
+      <c r="G136" s="11" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="n"/>
@@ -18763,6 +19062,7 @@
       <c r="D137" s="11" t="n"/>
       <c r="E137" s="11" t="n"/>
       <c r="F137" s="11" t="n"/>
+      <c r="G137" s="11" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="n"/>
@@ -18770,6 +19070,7 @@
       <c r="D138" s="11" t="n"/>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
+      <c r="G138" s="11" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="n"/>
@@ -18777,6 +19078,7 @@
       <c r="D139" s="11" t="n"/>
       <c r="E139" s="11" t="n"/>
       <c r="F139" s="11" t="n"/>
+      <c r="G139" s="11" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="n"/>
@@ -18784,6 +19086,7 @@
       <c r="D140" s="11" t="n"/>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
+      <c r="G140" s="11" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="n"/>
@@ -18791,6 +19094,7 @@
       <c r="D141" s="11" t="n"/>
       <c r="E141" s="11" t="n"/>
       <c r="F141" s="11" t="n"/>
+      <c r="G141" s="11" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="n"/>
@@ -18798,6 +19102,7 @@
       <c r="D142" s="11" t="n"/>
       <c r="E142" s="11" t="n"/>
       <c r="F142" s="11" t="n"/>
+      <c r="G142" s="11" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="n"/>
@@ -18805,6 +19110,7 @@
       <c r="D143" s="11" t="n"/>
       <c r="E143" s="11" t="n"/>
       <c r="F143" s="11" t="n"/>
+      <c r="G143" s="11" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="n"/>
@@ -18812,6 +19118,7 @@
       <c r="D144" s="11" t="n"/>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
+      <c r="G144" s="11" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="n"/>
@@ -18819,6 +19126,7 @@
       <c r="D145" s="11" t="n"/>
       <c r="E145" s="11" t="n"/>
       <c r="F145" s="11" t="n"/>
+      <c r="G145" s="11" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="n"/>
@@ -18826,6 +19134,7 @@
       <c r="D146" s="11" t="n"/>
       <c r="E146" s="11" t="n"/>
       <c r="F146" s="11" t="n"/>
+      <c r="G146" s="11" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="n"/>
@@ -18833,6 +19142,7 @@
       <c r="D147" s="11" t="n"/>
       <c r="E147" s="11" t="n"/>
       <c r="F147" s="11" t="n"/>
+      <c r="G147" s="11" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="n"/>
@@ -18840,6 +19150,7 @@
       <c r="D148" s="11" t="n"/>
       <c r="E148" s="11" t="n"/>
       <c r="F148" s="11" t="n"/>
+      <c r="G148" s="11" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="n"/>
@@ -18847,6 +19158,7 @@
       <c r="D149" s="11" t="n"/>
       <c r="E149" s="11" t="n"/>
       <c r="F149" s="11" t="n"/>
+      <c r="G149" s="11" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="n"/>
@@ -18854,6 +19166,7 @@
       <c r="D150" s="11" t="n"/>
       <c r="E150" s="11" t="n"/>
       <c r="F150" s="11" t="n"/>
+      <c r="G150" s="11" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="n"/>
@@ -18861,6 +19174,7 @@
       <c r="D151" s="11" t="n"/>
       <c r="E151" s="11" t="n"/>
       <c r="F151" s="11" t="n"/>
+      <c r="G151" s="11" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="n"/>
@@ -18868,6 +19182,7 @@
       <c r="D152" s="11" t="n"/>
       <c r="E152" s="11" t="n"/>
       <c r="F152" s="11" t="n"/>
+      <c r="G152" s="11" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="n"/>
@@ -18875,6 +19190,7 @@
       <c r="D153" s="11" t="n"/>
       <c r="E153" s="11" t="n"/>
       <c r="F153" s="11" t="n"/>
+      <c r="G153" s="11" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="n"/>
@@ -18882,6 +19198,7 @@
       <c r="D154" s="11" t="n"/>
       <c r="E154" s="11" t="n"/>
       <c r="F154" s="11" t="n"/>
+      <c r="G154" s="11" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="n"/>
@@ -18889,6 +19206,7 @@
       <c r="D155" s="11" t="n"/>
       <c r="E155" s="11" t="n"/>
       <c r="F155" s="11" t="n"/>
+      <c r="G155" s="11" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="n"/>
@@ -18896,6 +19214,7 @@
       <c r="D156" s="11" t="n"/>
       <c r="E156" s="11" t="n"/>
       <c r="F156" s="11" t="n"/>
+      <c r="G156" s="11" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="n"/>
@@ -18903,6 +19222,7 @@
       <c r="D157" s="11" t="n"/>
       <c r="E157" s="11" t="n"/>
       <c r="F157" s="11" t="n"/>
+      <c r="G157" s="11" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="n"/>
@@ -18910,6 +19230,7 @@
       <c r="D158" s="11" t="n"/>
       <c r="E158" s="11" t="n"/>
       <c r="F158" s="11" t="n"/>
+      <c r="G158" s="11" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="n"/>
@@ -18917,6 +19238,7 @@
       <c r="D159" s="11" t="n"/>
       <c r="E159" s="11" t="n"/>
       <c r="F159" s="11" t="n"/>
+      <c r="G159" s="11" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="n"/>
@@ -18924,6 +19246,7 @@
       <c r="D160" s="11" t="n"/>
       <c r="E160" s="11" t="n"/>
       <c r="F160" s="11" t="n"/>
+      <c r="G160" s="11" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="n"/>
@@ -18931,6 +19254,7 @@
       <c r="D161" s="11" t="n"/>
       <c r="E161" s="11" t="n"/>
       <c r="F161" s="11" t="n"/>
+      <c r="G161" s="11" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="11" t="n"/>
@@ -18938,6 +19262,7 @@
       <c r="D162" s="11" t="n"/>
       <c r="E162" s="11" t="n"/>
       <c r="F162" s="11" t="n"/>
+      <c r="G162" s="11" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="n"/>
@@ -18945,6 +19270,7 @@
       <c r="D163" s="11" t="n"/>
       <c r="E163" s="11" t="n"/>
       <c r="F163" s="11" t="n"/>
+      <c r="G163" s="11" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="n"/>
@@ -18952,6 +19278,7 @@
       <c r="D164" s="11" t="n"/>
       <c r="E164" s="11" t="n"/>
       <c r="F164" s="11" t="n"/>
+      <c r="G164" s="11" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="n"/>
@@ -18959,6 +19286,7 @@
       <c r="D165" s="11" t="n"/>
       <c r="E165" s="11" t="n"/>
       <c r="F165" s="11" t="n"/>
+      <c r="G165" s="11" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="n"/>
@@ -18966,6 +19294,7 @@
       <c r="D166" s="11" t="n"/>
       <c r="E166" s="11" t="n"/>
       <c r="F166" s="11" t="n"/>
+      <c r="G166" s="11" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="n"/>
@@ -18973,6 +19302,7 @@
       <c r="D167" s="11" t="n"/>
       <c r="E167" s="11" t="n"/>
       <c r="F167" s="11" t="n"/>
+      <c r="G167" s="11" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="n"/>
@@ -18980,6 +19310,7 @@
       <c r="D168" s="11" t="n"/>
       <c r="E168" s="11" t="n"/>
       <c r="F168" s="11" t="n"/>
+      <c r="G168" s="11" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="n"/>
@@ -18987,6 +19318,7 @@
       <c r="D169" s="11" t="n"/>
       <c r="E169" s="11" t="n"/>
       <c r="F169" s="11" t="n"/>
+      <c r="G169" s="11" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="n"/>
@@ -18994,6 +19326,7 @@
       <c r="D170" s="11" t="n"/>
       <c r="E170" s="11" t="n"/>
       <c r="F170" s="11" t="n"/>
+      <c r="G170" s="11" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="n"/>
@@ -19001,6 +19334,7 @@
       <c r="D171" s="11" t="n"/>
       <c r="E171" s="11" t="n"/>
       <c r="F171" s="11" t="n"/>
+      <c r="G171" s="11" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="n"/>
@@ -19008,6 +19342,7 @@
       <c r="D172" s="11" t="n"/>
       <c r="E172" s="11" t="n"/>
       <c r="F172" s="11" t="n"/>
+      <c r="G172" s="11" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="n"/>
@@ -19015,6 +19350,7 @@
       <c r="D173" s="11" t="n"/>
       <c r="E173" s="11" t="n"/>
       <c r="F173" s="11" t="n"/>
+      <c r="G173" s="11" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="n"/>
@@ -19022,6 +19358,7 @@
       <c r="D174" s="11" t="n"/>
       <c r="E174" s="11" t="n"/>
       <c r="F174" s="11" t="n"/>
+      <c r="G174" s="11" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="n"/>
@@ -19029,6 +19366,7 @@
       <c r="D175" s="11" t="n"/>
       <c r="E175" s="11" t="n"/>
       <c r="F175" s="11" t="n"/>
+      <c r="G175" s="11" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="n"/>
@@ -19036,6 +19374,7 @@
       <c r="D176" s="11" t="n"/>
       <c r="E176" s="11" t="n"/>
       <c r="F176" s="11" t="n"/>
+      <c r="G176" s="11" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="n"/>
@@ -19043,6 +19382,7 @@
       <c r="D177" s="11" t="n"/>
       <c r="E177" s="11" t="n"/>
       <c r="F177" s="11" t="n"/>
+      <c r="G177" s="11" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="n"/>
@@ -19050,6 +19390,7 @@
       <c r="D178" s="11" t="n"/>
       <c r="E178" s="11" t="n"/>
       <c r="F178" s="11" t="n"/>
+      <c r="G178" s="11" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="n"/>
@@ -19057,6 +19398,7 @@
       <c r="D179" s="11" t="n"/>
       <c r="E179" s="11" t="n"/>
       <c r="F179" s="11" t="n"/>
+      <c r="G179" s="11" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="n"/>
@@ -19064,6 +19406,7 @@
       <c r="D180" s="11" t="n"/>
       <c r="E180" s="11" t="n"/>
       <c r="F180" s="11" t="n"/>
+      <c r="G180" s="11" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="n"/>
@@ -19071,6 +19414,7 @@
       <c r="D181" s="11" t="n"/>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
+      <c r="G181" s="11" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="n"/>
@@ -19078,6 +19422,7 @@
       <c r="D182" s="11" t="n"/>
       <c r="E182" s="11" t="n"/>
       <c r="F182" s="11" t="n"/>
+      <c r="G182" s="11" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="n"/>
@@ -19085,6 +19430,7 @@
       <c r="D183" s="11" t="n"/>
       <c r="E183" s="11" t="n"/>
       <c r="F183" s="11" t="n"/>
+      <c r="G183" s="11" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="n"/>
@@ -19092,6 +19438,7 @@
       <c r="D184" s="11" t="n"/>
       <c r="E184" s="11" t="n"/>
       <c r="F184" s="11" t="n"/>
+      <c r="G184" s="11" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="n"/>
@@ -19099,6 +19446,7 @@
       <c r="D185" s="11" t="n"/>
       <c r="E185" s="11" t="n"/>
       <c r="F185" s="11" t="n"/>
+      <c r="G185" s="11" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="n"/>
@@ -19106,6 +19454,7 @@
       <c r="D186" s="11" t="n"/>
       <c r="E186" s="11" t="n"/>
       <c r="F186" s="11" t="n"/>
+      <c r="G186" s="11" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="n"/>
@@ -19113,6 +19462,7 @@
       <c r="D187" s="11" t="n"/>
       <c r="E187" s="11" t="n"/>
       <c r="F187" s="11" t="n"/>
+      <c r="G187" s="11" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="n"/>
@@ -19120,6 +19470,7 @@
       <c r="D188" s="11" t="n"/>
       <c r="E188" s="11" t="n"/>
       <c r="F188" s="11" t="n"/>
+      <c r="G188" s="11" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="n"/>
@@ -19127,6 +19478,7 @@
       <c r="D189" s="11" t="n"/>
       <c r="E189" s="11" t="n"/>
       <c r="F189" s="11" t="n"/>
+      <c r="G189" s="11" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="n"/>
@@ -19134,6 +19486,7 @@
       <c r="D190" s="11" t="n"/>
       <c r="E190" s="11" t="n"/>
       <c r="F190" s="11" t="n"/>
+      <c r="G190" s="11" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="n"/>
@@ -19141,6 +19494,7 @@
       <c r="D191" s="11" t="n"/>
       <c r="E191" s="11" t="n"/>
       <c r="F191" s="11" t="n"/>
+      <c r="G191" s="11" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="n"/>
@@ -19148,6 +19502,7 @@
       <c r="D192" s="11" t="n"/>
       <c r="E192" s="11" t="n"/>
       <c r="F192" s="11" t="n"/>
+      <c r="G192" s="11" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="n"/>
@@ -19155,6 +19510,7 @@
       <c r="D193" s="11" t="n"/>
       <c r="E193" s="11" t="n"/>
       <c r="F193" s="11" t="n"/>
+      <c r="G193" s="11" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="n"/>
@@ -19162,6 +19518,7 @@
       <c r="D194" s="11" t="n"/>
       <c r="E194" s="11" t="n"/>
       <c r="F194" s="11" t="n"/>
+      <c r="G194" s="11" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="n"/>
@@ -19169,6 +19526,7 @@
       <c r="D195" s="11" t="n"/>
       <c r="E195" s="11" t="n"/>
       <c r="F195" s="11" t="n"/>
+      <c r="G195" s="11" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="n"/>
@@ -19176,6 +19534,7 @@
       <c r="D196" s="11" t="n"/>
       <c r="E196" s="11" t="n"/>
       <c r="F196" s="11" t="n"/>
+      <c r="G196" s="11" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="n"/>
@@ -19183,6 +19542,7 @@
       <c r="D197" s="11" t="n"/>
       <c r="E197" s="11" t="n"/>
       <c r="F197" s="11" t="n"/>
+      <c r="G197" s="11" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="n"/>
@@ -19190,6 +19550,7 @@
       <c r="D198" s="11" t="n"/>
       <c r="E198" s="11" t="n"/>
       <c r="F198" s="11" t="n"/>
+      <c r="G198" s="11" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="n"/>
@@ -19197,6 +19558,7 @@
       <c r="D199" s="11" t="n"/>
       <c r="E199" s="11" t="n"/>
       <c r="F199" s="11" t="n"/>
+      <c r="G199" s="11" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="n"/>
@@ -19204,6 +19566,7 @@
       <c r="D200" s="11" t="n"/>
       <c r="E200" s="11" t="n"/>
       <c r="F200" s="11" t="n"/>
+      <c r="G200" s="11" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="n"/>
@@ -19211,6 +19574,7 @@
       <c r="D201" s="11" t="n"/>
       <c r="E201" s="11" t="n"/>
       <c r="F201" s="11" t="n"/>
+      <c r="G201" s="11" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="n"/>
@@ -19218,6 +19582,7 @@
       <c r="D202" s="11" t="n"/>
       <c r="E202" s="11" t="n"/>
       <c r="F202" s="11" t="n"/>
+      <c r="G202" s="11" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="n"/>
@@ -19225,6 +19590,7 @@
       <c r="D203" s="11" t="n"/>
       <c r="E203" s="11" t="n"/>
       <c r="F203" s="11" t="n"/>
+      <c r="G203" s="11" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="n"/>
@@ -19232,6 +19598,7 @@
       <c r="D204" s="11" t="n"/>
       <c r="E204" s="11" t="n"/>
       <c r="F204" s="11" t="n"/>
+      <c r="G204" s="11" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="n"/>
@@ -19239,6 +19606,7 @@
       <c r="D205" s="11" t="n"/>
       <c r="E205" s="11" t="n"/>
       <c r="F205" s="11" t="n"/>
+      <c r="G205" s="11" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="n"/>
@@ -19246,6 +19614,7 @@
       <c r="D206" s="11" t="n"/>
       <c r="E206" s="11" t="n"/>
       <c r="F206" s="11" t="n"/>
+      <c r="G206" s="11" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="n"/>
@@ -19253,6 +19622,7 @@
       <c r="D207" s="11" t="n"/>
       <c r="E207" s="11" t="n"/>
       <c r="F207" s="11" t="n"/>
+      <c r="G207" s="11" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="n"/>
@@ -19260,6 +19630,7 @@
       <c r="D208" s="11" t="n"/>
       <c r="E208" s="11" t="n"/>
       <c r="F208" s="11" t="n"/>
+      <c r="G208" s="11" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="n"/>
@@ -19267,6 +19638,7 @@
       <c r="D209" s="11" t="n"/>
       <c r="E209" s="11" t="n"/>
       <c r="F209" s="11" t="n"/>
+      <c r="G209" s="11" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="n"/>
@@ -19274,6 +19646,7 @@
       <c r="D210" s="11" t="n"/>
       <c r="E210" s="11" t="n"/>
       <c r="F210" s="11" t="n"/>
+      <c r="G210" s="11" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="n"/>
@@ -19281,6 +19654,7 @@
       <c r="D211" s="11" t="n"/>
       <c r="E211" s="11" t="n"/>
       <c r="F211" s="11" t="n"/>
+      <c r="G211" s="11" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="n"/>
@@ -19288,6 +19662,7 @@
       <c r="D212" s="11" t="n"/>
       <c r="E212" s="11" t="n"/>
       <c r="F212" s="11" t="n"/>
+      <c r="G212" s="11" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="n"/>
@@ -19295,6 +19670,7 @@
       <c r="D213" s="11" t="n"/>
       <c r="E213" s="11" t="n"/>
       <c r="F213" s="11" t="n"/>
+      <c r="G213" s="11" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="n"/>
@@ -19302,6 +19678,7 @@
       <c r="D214" s="11" t="n"/>
       <c r="E214" s="11" t="n"/>
       <c r="F214" s="11" t="n"/>
+      <c r="G214" s="11" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="n"/>
@@ -19309,6 +19686,7 @@
       <c r="D215" s="11" t="n"/>
       <c r="E215" s="11" t="n"/>
       <c r="F215" s="11" t="n"/>
+      <c r="G215" s="11" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="n"/>
@@ -19316,6 +19694,7 @@
       <c r="D216" s="11" t="n"/>
       <c r="E216" s="11" t="n"/>
       <c r="F216" s="11" t="n"/>
+      <c r="G216" s="11" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="n"/>
@@ -19323,6 +19702,7 @@
       <c r="D217" s="11" t="n"/>
       <c r="E217" s="11" t="n"/>
       <c r="F217" s="11" t="n"/>
+      <c r="G217" s="11" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="n"/>
@@ -19330,6 +19710,7 @@
       <c r="D218" s="11" t="n"/>
       <c r="E218" s="11" t="n"/>
       <c r="F218" s="11" t="n"/>
+      <c r="G218" s="11" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="n"/>
@@ -19337,6 +19718,7 @@
       <c r="D219" s="11" t="n"/>
       <c r="E219" s="11" t="n"/>
       <c r="F219" s="11" t="n"/>
+      <c r="G219" s="11" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="n"/>
@@ -19344,6 +19726,7 @@
       <c r="D220" s="11" t="n"/>
       <c r="E220" s="11" t="n"/>
       <c r="F220" s="11" t="n"/>
+      <c r="G220" s="11" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="n"/>
@@ -19351,6 +19734,7 @@
       <c r="D221" s="11" t="n"/>
       <c r="E221" s="11" t="n"/>
       <c r="F221" s="11" t="n"/>
+      <c r="G221" s="11" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="n"/>
@@ -19358,6 +19742,7 @@
       <c r="D222" s="11" t="n"/>
       <c r="E222" s="11" t="n"/>
       <c r="F222" s="11" t="n"/>
+      <c r="G222" s="11" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="n"/>
@@ -19365,6 +19750,7 @@
       <c r="D223" s="11" t="n"/>
       <c r="E223" s="11" t="n"/>
       <c r="F223" s="11" t="n"/>
+      <c r="G223" s="11" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="n"/>
@@ -19372,6 +19758,7 @@
       <c r="D224" s="11" t="n"/>
       <c r="E224" s="11" t="n"/>
       <c r="F224" s="11" t="n"/>
+      <c r="G224" s="11" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="n"/>
@@ -19379,6 +19766,7 @@
       <c r="D225" s="11" t="n"/>
       <c r="E225" s="11" t="n"/>
       <c r="F225" s="11" t="n"/>
+      <c r="G225" s="11" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="n"/>
@@ -19386,6 +19774,7 @@
       <c r="D226" s="11" t="n"/>
       <c r="E226" s="11" t="n"/>
       <c r="F226" s="11" t="n"/>
+      <c r="G226" s="11" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="n"/>
@@ -19393,6 +19782,7 @@
       <c r="D227" s="11" t="n"/>
       <c r="E227" s="11" t="n"/>
       <c r="F227" s="11" t="n"/>
+      <c r="G227" s="11" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="n"/>
@@ -19400,6 +19790,7 @@
       <c r="D228" s="11" t="n"/>
       <c r="E228" s="11" t="n"/>
       <c r="F228" s="11" t="n"/>
+      <c r="G228" s="11" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="n"/>
@@ -19407,6 +19798,7 @@
       <c r="D229" s="11" t="n"/>
       <c r="E229" s="11" t="n"/>
       <c r="F229" s="11" t="n"/>
+      <c r="G229" s="11" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="n"/>
@@ -19414,6 +19806,7 @@
       <c r="D230" s="11" t="n"/>
       <c r="E230" s="11" t="n"/>
       <c r="F230" s="11" t="n"/>
+      <c r="G230" s="11" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="n"/>
@@ -19421,6 +19814,7 @@
       <c r="D231" s="11" t="n"/>
       <c r="E231" s="11" t="n"/>
       <c r="F231" s="11" t="n"/>
+      <c r="G231" s="11" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="n"/>
@@ -19428,6 +19822,7 @@
       <c r="D232" s="11" t="n"/>
       <c r="E232" s="11" t="n"/>
       <c r="F232" s="11" t="n"/>
+      <c r="G232" s="11" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="n"/>
@@ -19435,6 +19830,7 @@
       <c r="D233" s="11" t="n"/>
       <c r="E233" s="11" t="n"/>
       <c r="F233" s="11" t="n"/>
+      <c r="G233" s="11" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="n"/>
@@ -19442,6 +19838,7 @@
       <c r="D234" s="11" t="n"/>
       <c r="E234" s="11" t="n"/>
       <c r="F234" s="11" t="n"/>
+      <c r="G234" s="11" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="11" t="n"/>
@@ -19449,6 +19846,7 @@
       <c r="D235" s="11" t="n"/>
       <c r="E235" s="11" t="n"/>
       <c r="F235" s="11" t="n"/>
+      <c r="G235" s="11" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="11" t="n"/>
@@ -19456,6 +19854,7 @@
       <c r="D236" s="11" t="n"/>
       <c r="E236" s="11" t="n"/>
       <c r="F236" s="11" t="n"/>
+      <c r="G236" s="11" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="n"/>
@@ -19463,6 +19862,7 @@
       <c r="D237" s="11" t="n"/>
       <c r="E237" s="11" t="n"/>
       <c r="F237" s="11" t="n"/>
+      <c r="G237" s="11" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="n"/>
@@ -19470,6 +19870,7 @@
       <c r="D238" s="11" t="n"/>
       <c r="E238" s="11" t="n"/>
       <c r="F238" s="11" t="n"/>
+      <c r="G238" s="11" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="n"/>
@@ -19477,6 +19878,7 @@
       <c r="D239" s="11" t="n"/>
       <c r="E239" s="11" t="n"/>
       <c r="F239" s="11" t="n"/>
+      <c r="G239" s="11" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="n"/>
@@ -19484,6 +19886,7 @@
       <c r="D240" s="11" t="n"/>
       <c r="E240" s="11" t="n"/>
       <c r="F240" s="11" t="n"/>
+      <c r="G240" s="11" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="n"/>
@@ -19491,6 +19894,7 @@
       <c r="D241" s="11" t="n"/>
       <c r="E241" s="11" t="n"/>
       <c r="F241" s="11" t="n"/>
+      <c r="G241" s="11" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="n"/>
@@ -19498,6 +19902,7 @@
       <c r="D242" s="11" t="n"/>
       <c r="E242" s="11" t="n"/>
       <c r="F242" s="11" t="n"/>
+      <c r="G242" s="11" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="n"/>
@@ -19505,6 +19910,7 @@
       <c r="D243" s="11" t="n"/>
       <c r="E243" s="11" t="n"/>
       <c r="F243" s="11" t="n"/>
+      <c r="G243" s="11" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="n"/>
@@ -19512,6 +19918,7 @@
       <c r="D244" s="11" t="n"/>
       <c r="E244" s="11" t="n"/>
       <c r="F244" s="11" t="n"/>
+      <c r="G244" s="11" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="11" t="n"/>
@@ -19519,6 +19926,7 @@
       <c r="D245" s="11" t="n"/>
       <c r="E245" s="11" t="n"/>
       <c r="F245" s="11" t="n"/>
+      <c r="G245" s="11" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="11" t="n"/>
@@ -19526,6 +19934,7 @@
       <c r="D246" s="11" t="n"/>
       <c r="E246" s="11" t="n"/>
       <c r="F246" s="11" t="n"/>
+      <c r="G246" s="11" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="n"/>
@@ -19533,6 +19942,7 @@
       <c r="D247" s="11" t="n"/>
       <c r="E247" s="11" t="n"/>
       <c r="F247" s="11" t="n"/>
+      <c r="G247" s="11" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="n"/>
@@ -19540,6 +19950,7 @@
       <c r="D248" s="11" t="n"/>
       <c r="E248" s="11" t="n"/>
       <c r="F248" s="11" t="n"/>
+      <c r="G248" s="11" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="n"/>
@@ -19547,6 +19958,7 @@
       <c r="D249" s="11" t="n"/>
       <c r="E249" s="11" t="n"/>
       <c r="F249" s="11" t="n"/>
+      <c r="G249" s="11" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="n"/>
@@ -19554,6 +19966,7 @@
       <c r="D250" s="11" t="n"/>
       <c r="E250" s="11" t="n"/>
       <c r="F250" s="11" t="n"/>
+      <c r="G250" s="11" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="11" t="n"/>
@@ -19561,6 +19974,7 @@
       <c r="D251" s="11" t="n"/>
       <c r="E251" s="11" t="n"/>
       <c r="F251" s="11" t="n"/>
+      <c r="G251" s="11" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="n"/>
@@ -19568,6 +19982,7 @@
       <c r="D252" s="11" t="n"/>
       <c r="E252" s="11" t="n"/>
       <c r="F252" s="11" t="n"/>
+      <c r="G252" s="11" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="n"/>
@@ -19575,6 +19990,7 @@
       <c r="D253" s="11" t="n"/>
       <c r="E253" s="11" t="n"/>
       <c r="F253" s="11" t="n"/>
+      <c r="G253" s="11" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="n"/>
@@ -19582,6 +19998,7 @@
       <c r="D254" s="11" t="n"/>
       <c r="E254" s="11" t="n"/>
       <c r="F254" s="11" t="n"/>
+      <c r="G254" s="11" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="n"/>
@@ -19589,6 +20006,7 @@
       <c r="D255" s="11" t="n"/>
       <c r="E255" s="11" t="n"/>
       <c r="F255" s="11" t="n"/>
+      <c r="G255" s="11" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="n"/>
@@ -19596,6 +20014,7 @@
       <c r="D256" s="11" t="n"/>
       <c r="E256" s="11" t="n"/>
       <c r="F256" s="11" t="n"/>
+      <c r="G256" s="11" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="11" t="n"/>
@@ -19603,6 +20022,7 @@
       <c r="D257" s="11" t="n"/>
       <c r="E257" s="11" t="n"/>
       <c r="F257" s="11" t="n"/>
+      <c r="G257" s="11" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="11" t="n"/>
@@ -19610,6 +20030,7 @@
       <c r="D258" s="11" t="n"/>
       <c r="E258" s="11" t="n"/>
       <c r="F258" s="11" t="n"/>
+      <c r="G258" s="11" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="11" t="n"/>
@@ -19617,6 +20038,7 @@
       <c r="D259" s="11" t="n"/>
       <c r="E259" s="11" t="n"/>
       <c r="F259" s="11" t="n"/>
+      <c r="G259" s="11" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="n"/>
@@ -19624,6 +20046,7 @@
       <c r="D260" s="11" t="n"/>
       <c r="E260" s="11" t="n"/>
       <c r="F260" s="11" t="n"/>
+      <c r="G260" s="11" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="11" t="n"/>
@@ -19631,6 +20054,7 @@
       <c r="D261" s="11" t="n"/>
       <c r="E261" s="11" t="n"/>
       <c r="F261" s="11" t="n"/>
+      <c r="G261" s="11" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="11" t="n"/>
@@ -19638,6 +20062,7 @@
       <c r="D262" s="11" t="n"/>
       <c r="E262" s="11" t="n"/>
       <c r="F262" s="11" t="n"/>
+      <c r="G262" s="11" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="11" t="n"/>
@@ -19645,6 +20070,7 @@
       <c r="D263" s="11" t="n"/>
       <c r="E263" s="11" t="n"/>
       <c r="F263" s="11" t="n"/>
+      <c r="G263" s="11" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="n"/>
@@ -19652,6 +20078,7 @@
       <c r="D264" s="11" t="n"/>
       <c r="E264" s="11" t="n"/>
       <c r="F264" s="11" t="n"/>
+      <c r="G264" s="11" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="11" t="n"/>
@@ -19659,6 +20086,7 @@
       <c r="D265" s="11" t="n"/>
       <c r="E265" s="11" t="n"/>
       <c r="F265" s="11" t="n"/>
+      <c r="G265" s="11" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="n"/>
@@ -19666,6 +20094,7 @@
       <c r="D266" s="11" t="n"/>
       <c r="E266" s="11" t="n"/>
       <c r="F266" s="11" t="n"/>
+      <c r="G266" s="11" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="n"/>
@@ -19673,6 +20102,7 @@
       <c r="D267" s="11" t="n"/>
       <c r="E267" s="11" t="n"/>
       <c r="F267" s="11" t="n"/>
+      <c r="G267" s="11" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="n"/>
@@ -19680,6 +20110,7 @@
       <c r="D268" s="11" t="n"/>
       <c r="E268" s="11" t="n"/>
       <c r="F268" s="11" t="n"/>
+      <c r="G268" s="11" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="n"/>
@@ -19687,6 +20118,7 @@
       <c r="D269" s="11" t="n"/>
       <c r="E269" s="11" t="n"/>
       <c r="F269" s="11" t="n"/>
+      <c r="G269" s="11" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="n"/>
@@ -19694,6 +20126,7 @@
       <c r="D270" s="11" t="n"/>
       <c r="E270" s="11" t="n"/>
       <c r="F270" s="11" t="n"/>
+      <c r="G270" s="11" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="n"/>
@@ -19701,6 +20134,7 @@
       <c r="D271" s="11" t="n"/>
       <c r="E271" s="11" t="n"/>
       <c r="F271" s="11" t="n"/>
+      <c r="G271" s="11" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="11" t="n"/>
@@ -19708,6 +20142,7 @@
       <c r="D272" s="11" t="n"/>
       <c r="E272" s="11" t="n"/>
       <c r="F272" s="11" t="n"/>
+      <c r="G272" s="11" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="11" t="n"/>
@@ -19715,6 +20150,7 @@
       <c r="D273" s="11" t="n"/>
       <c r="E273" s="11" t="n"/>
       <c r="F273" s="11" t="n"/>
+      <c r="G273" s="11" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="11" t="n"/>
@@ -19722,6 +20158,7 @@
       <c r="D274" s="11" t="n"/>
       <c r="E274" s="11" t="n"/>
       <c r="F274" s="11" t="n"/>
+      <c r="G274" s="11" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="11" t="n"/>
@@ -19729,6 +20166,7 @@
       <c r="D275" s="11" t="n"/>
       <c r="E275" s="11" t="n"/>
       <c r="F275" s="11" t="n"/>
+      <c r="G275" s="11" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="n"/>
@@ -19736,6 +20174,7 @@
       <c r="D276" s="11" t="n"/>
       <c r="E276" s="11" t="n"/>
       <c r="F276" s="11" t="n"/>
+      <c r="G276" s="11" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="11" t="n"/>
@@ -19743,6 +20182,7 @@
       <c r="D277" s="11" t="n"/>
       <c r="E277" s="11" t="n"/>
       <c r="F277" s="11" t="n"/>
+      <c r="G277" s="11" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="11" t="n"/>
@@ -19750,6 +20190,7 @@
       <c r="D278" s="11" t="n"/>
       <c r="E278" s="11" t="n"/>
       <c r="F278" s="11" t="n"/>
+      <c r="G278" s="11" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="11" t="n"/>
@@ -19757,6 +20198,7 @@
       <c r="D279" s="11" t="n"/>
       <c r="E279" s="11" t="n"/>
       <c r="F279" s="11" t="n"/>
+      <c r="G279" s="11" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="11" t="n"/>
@@ -19764,6 +20206,7 @@
       <c r="D280" s="11" t="n"/>
       <c r="E280" s="11" t="n"/>
       <c r="F280" s="11" t="n"/>
+      <c r="G280" s="11" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="11" t="n"/>
@@ -19771,6 +20214,7 @@
       <c r="D281" s="11" t="n"/>
       <c r="E281" s="11" t="n"/>
       <c r="F281" s="11" t="n"/>
+      <c r="G281" s="11" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="11" t="n"/>
@@ -19778,6 +20222,7 @@
       <c r="D282" s="11" t="n"/>
       <c r="E282" s="11" t="n"/>
       <c r="F282" s="11" t="n"/>
+      <c r="G282" s="11" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="11" t="n"/>
@@ -19785,6 +20230,7 @@
       <c r="D283" s="11" t="n"/>
       <c r="E283" s="11" t="n"/>
       <c r="F283" s="11" t="n"/>
+      <c r="G283" s="11" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="n"/>
@@ -19792,6 +20238,7 @@
       <c r="D284" s="11" t="n"/>
       <c r="E284" s="11" t="n"/>
       <c r="F284" s="11" t="n"/>
+      <c r="G284" s="11" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="n"/>
@@ -19799,6 +20246,7 @@
       <c r="D285" s="11" t="n"/>
       <c r="E285" s="11" t="n"/>
       <c r="F285" s="11" t="n"/>
+      <c r="G285" s="11" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="n"/>
@@ -19806,6 +20254,7 @@
       <c r="D286" s="11" t="n"/>
       <c r="E286" s="11" t="n"/>
       <c r="F286" s="11" t="n"/>
+      <c r="G286" s="11" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="11" t="n"/>
@@ -19813,6 +20262,7 @@
       <c r="D287" s="11" t="n"/>
       <c r="E287" s="11" t="n"/>
       <c r="F287" s="11" t="n"/>
+      <c r="G287" s="11" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="11" t="n"/>
@@ -19820,6 +20270,7 @@
       <c r="D288" s="11" t="n"/>
       <c r="E288" s="11" t="n"/>
       <c r="F288" s="11" t="n"/>
+      <c r="G288" s="11" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="11" t="n"/>
@@ -19827,6 +20278,7 @@
       <c r="D289" s="11" t="n"/>
       <c r="E289" s="11" t="n"/>
       <c r="F289" s="11" t="n"/>
+      <c r="G289" s="11" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="11" t="n"/>
@@ -19834,6 +20286,7 @@
       <c r="D290" s="11" t="n"/>
       <c r="E290" s="11" t="n"/>
       <c r="F290" s="11" t="n"/>
+      <c r="G290" s="11" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="11" t="n"/>
@@ -19841,6 +20294,7 @@
       <c r="D291" s="11" t="n"/>
       <c r="E291" s="11" t="n"/>
       <c r="F291" s="11" t="n"/>
+      <c r="G291" s="11" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="n"/>
@@ -19848,6 +20302,7 @@
       <c r="D292" s="11" t="n"/>
       <c r="E292" s="11" t="n"/>
       <c r="F292" s="11" t="n"/>
+      <c r="G292" s="11" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="11" t="n"/>
@@ -19855,6 +20310,7 @@
       <c r="D293" s="11" t="n"/>
       <c r="E293" s="11" t="n"/>
       <c r="F293" s="11" t="n"/>
+      <c r="G293" s="11" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="11" t="n"/>
@@ -19862,6 +20318,7 @@
       <c r="D294" s="11" t="n"/>
       <c r="E294" s="11" t="n"/>
       <c r="F294" s="11" t="n"/>
+      <c r="G294" s="11" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="11" t="n"/>
@@ -19869,6 +20326,7 @@
       <c r="D295" s="11" t="n"/>
       <c r="E295" s="11" t="n"/>
       <c r="F295" s="11" t="n"/>
+      <c r="G295" s="11" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="11" t="n"/>
@@ -19876,6 +20334,7 @@
       <c r="D296" s="11" t="n"/>
       <c r="E296" s="11" t="n"/>
       <c r="F296" s="11" t="n"/>
+      <c r="G296" s="11" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="11" t="n"/>
@@ -19883,6 +20342,7 @@
       <c r="D297" s="11" t="n"/>
       <c r="E297" s="11" t="n"/>
       <c r="F297" s="11" t="n"/>
+      <c r="G297" s="11" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="11" t="n"/>
@@ -19890,6 +20350,7 @@
       <c r="D298" s="11" t="n"/>
       <c r="E298" s="11" t="n"/>
       <c r="F298" s="11" t="n"/>
+      <c r="G298" s="11" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="n"/>
@@ -19897,6 +20358,7 @@
       <c r="D299" s="11" t="n"/>
       <c r="E299" s="11" t="n"/>
       <c r="F299" s="11" t="n"/>
+      <c r="G299" s="11" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="n"/>
@@ -19904,6 +20366,7 @@
       <c r="D300" s="11" t="n"/>
       <c r="E300" s="11" t="n"/>
       <c r="F300" s="11" t="n"/>
+      <c r="G300" s="11" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="n"/>
@@ -19911,6 +20374,7 @@
       <c r="D301" s="11" t="n"/>
       <c r="E301" s="11" t="n"/>
       <c r="F301" s="11" t="n"/>
+      <c r="G301" s="11" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="11" t="n"/>
@@ -19918,6 +20382,7 @@
       <c r="D302" s="11" t="n"/>
       <c r="E302" s="11" t="n"/>
       <c r="F302" s="11" t="n"/>
+      <c r="G302" s="11" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="n"/>
@@ -19925,6 +20390,7 @@
       <c r="D303" s="11" t="n"/>
       <c r="E303" s="11" t="n"/>
       <c r="F303" s="11" t="n"/>
+      <c r="G303" s="11" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="n"/>
@@ -19932,6 +20398,7 @@
       <c r="D304" s="11" t="n"/>
       <c r="E304" s="11" t="n"/>
       <c r="F304" s="11" t="n"/>
+      <c r="G304" s="11" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="n"/>
@@ -19939,6 +20406,7 @@
       <c r="D305" s="11" t="n"/>
       <c r="E305" s="11" t="n"/>
       <c r="F305" s="11" t="n"/>
+      <c r="G305" s="11" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="n"/>
@@ -19946,6 +20414,7 @@
       <c r="D306" s="11" t="n"/>
       <c r="E306" s="11" t="n"/>
       <c r="F306" s="11" t="n"/>
+      <c r="G306" s="11" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="n"/>
@@ -19953,6 +20422,7 @@
       <c r="D307" s="11" t="n"/>
       <c r="E307" s="11" t="n"/>
       <c r="F307" s="11" t="n"/>
+      <c r="G307" s="11" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="n"/>
@@ -19960,6 +20430,7 @@
       <c r="D308" s="11" t="n"/>
       <c r="E308" s="11" t="n"/>
       <c r="F308" s="11" t="n"/>
+      <c r="G308" s="11" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="11" t="n"/>
@@ -19967,6 +20438,7 @@
       <c r="D309" s="11" t="n"/>
       <c r="E309" s="11" t="n"/>
       <c r="F309" s="11" t="n"/>
+      <c r="G309" s="11" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="11" t="n"/>
@@ -19974,6 +20446,7 @@
       <c r="D310" s="11" t="n"/>
       <c r="E310" s="11" t="n"/>
       <c r="F310" s="11" t="n"/>
+      <c r="G310" s="11" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="11" t="n"/>
@@ -19981,6 +20454,7 @@
       <c r="D311" s="11" t="n"/>
       <c r="E311" s="11" t="n"/>
       <c r="F311" s="11" t="n"/>
+      <c r="G311" s="11" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="n"/>
@@ -19988,6 +20462,7 @@
       <c r="D312" s="11" t="n"/>
       <c r="E312" s="11" t="n"/>
       <c r="F312" s="11" t="n"/>
+      <c r="G312" s="11" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="n"/>
@@ -19995,6 +20470,7 @@
       <c r="D313" s="11" t="n"/>
       <c r="E313" s="11" t="n"/>
       <c r="F313" s="11" t="n"/>
+      <c r="G313" s="11" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="11" t="n"/>
@@ -20002,6 +20478,7 @@
       <c r="D314" s="11" t="n"/>
       <c r="E314" s="11" t="n"/>
       <c r="F314" s="11" t="n"/>
+      <c r="G314" s="11" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="11" t="n"/>
@@ -20009,6 +20486,7 @@
       <c r="D315" s="11" t="n"/>
       <c r="E315" s="11" t="n"/>
       <c r="F315" s="11" t="n"/>
+      <c r="G315" s="11" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="11" t="n"/>
@@ -20016,6 +20494,7 @@
       <c r="D316" s="11" t="n"/>
       <c r="E316" s="11" t="n"/>
       <c r="F316" s="11" t="n"/>
+      <c r="G316" s="11" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="11" t="n"/>
@@ -20023,6 +20502,7 @@
       <c r="D317" s="11" t="n"/>
       <c r="E317" s="11" t="n"/>
       <c r="F317" s="11" t="n"/>
+      <c r="G317" s="11" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="11" t="n"/>
@@ -20030,6 +20510,7 @@
       <c r="D318" s="11" t="n"/>
       <c r="E318" s="11" t="n"/>
       <c r="F318" s="11" t="n"/>
+      <c r="G318" s="11" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="11" t="n"/>
@@ -20037,6 +20518,7 @@
       <c r="D319" s="11" t="n"/>
       <c r="E319" s="11" t="n"/>
       <c r="F319" s="11" t="n"/>
+      <c r="G319" s="11" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="11" t="n"/>
@@ -20044,6 +20526,7 @@
       <c r="D320" s="11" t="n"/>
       <c r="E320" s="11" t="n"/>
       <c r="F320" s="11" t="n"/>
+      <c r="G320" s="11" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="n"/>
@@ -20051,6 +20534,7 @@
       <c r="D321" s="11" t="n"/>
       <c r="E321" s="11" t="n"/>
       <c r="F321" s="11" t="n"/>
+      <c r="G321" s="11" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="11" t="n"/>
@@ -20058,6 +20542,7 @@
       <c r="D322" s="11" t="n"/>
       <c r="E322" s="11" t="n"/>
       <c r="F322" s="11" t="n"/>
+      <c r="G322" s="11" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="11" t="n"/>
@@ -20065,6 +20550,7 @@
       <c r="D323" s="11" t="n"/>
       <c r="E323" s="11" t="n"/>
       <c r="F323" s="11" t="n"/>
+      <c r="G323" s="11" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="11" t="n"/>
@@ -20072,6 +20558,7 @@
       <c r="D324" s="11" t="n"/>
       <c r="E324" s="11" t="n"/>
       <c r="F324" s="11" t="n"/>
+      <c r="G324" s="11" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="11" t="n"/>
@@ -20079,6 +20566,7 @@
       <c r="D325" s="11" t="n"/>
       <c r="E325" s="11" t="n"/>
       <c r="F325" s="11" t="n"/>
+      <c r="G325" s="11" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="11" t="n"/>
@@ -20086,6 +20574,7 @@
       <c r="D326" s="11" t="n"/>
       <c r="E326" s="11" t="n"/>
       <c r="F326" s="11" t="n"/>
+      <c r="G326" s="11" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="11" t="n"/>
@@ -20093,6 +20582,7 @@
       <c r="D327" s="11" t="n"/>
       <c r="E327" s="11" t="n"/>
       <c r="F327" s="11" t="n"/>
+      <c r="G327" s="11" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="11" t="n"/>
@@ -20100,6 +20590,7 @@
       <c r="D328" s="11" t="n"/>
       <c r="E328" s="11" t="n"/>
       <c r="F328" s="11" t="n"/>
+      <c r="G328" s="11" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="11" t="n"/>
@@ -20107,6 +20598,7 @@
       <c r="D329" s="11" t="n"/>
       <c r="E329" s="11" t="n"/>
       <c r="F329" s="11" t="n"/>
+      <c r="G329" s="11" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="11" t="n"/>
@@ -20114,6 +20606,7 @@
       <c r="D330" s="11" t="n"/>
       <c r="E330" s="11" t="n"/>
       <c r="F330" s="11" t="n"/>
+      <c r="G330" s="11" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="11" t="n"/>
@@ -20121,6 +20614,7 @@
       <c r="D331" s="11" t="n"/>
       <c r="E331" s="11" t="n"/>
       <c r="F331" s="11" t="n"/>
+      <c r="G331" s="11" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="11" t="n"/>
@@ -20128,6 +20622,7 @@
       <c r="D332" s="11" t="n"/>
       <c r="E332" s="11" t="n"/>
       <c r="F332" s="11" t="n"/>
+      <c r="G332" s="11" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="11" t="n"/>
@@ -20135,6 +20630,7 @@
       <c r="D333" s="11" t="n"/>
       <c r="E333" s="11" t="n"/>
       <c r="F333" s="11" t="n"/>
+      <c r="G333" s="11" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="11" t="n"/>
@@ -20142,6 +20638,7 @@
       <c r="D334" s="11" t="n"/>
       <c r="E334" s="11" t="n"/>
       <c r="F334" s="11" t="n"/>
+      <c r="G334" s="11" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="11" t="n"/>
@@ -20149,6 +20646,7 @@
       <c r="D335" s="11" t="n"/>
       <c r="E335" s="11" t="n"/>
       <c r="F335" s="11" t="n"/>
+      <c r="G335" s="11" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="11" t="n"/>
@@ -20156,6 +20654,7 @@
       <c r="D336" s="11" t="n"/>
       <c r="E336" s="11" t="n"/>
       <c r="F336" s="11" t="n"/>
+      <c r="G336" s="11" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="n"/>
@@ -20163,6 +20662,7 @@
       <c r="D337" s="11" t="n"/>
       <c r="E337" s="11" t="n"/>
       <c r="F337" s="11" t="n"/>
+      <c r="G337" s="11" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="11" t="n"/>
@@ -20170,6 +20670,7 @@
       <c r="D338" s="11" t="n"/>
       <c r="E338" s="11" t="n"/>
       <c r="F338" s="11" t="n"/>
+      <c r="G338" s="11" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="11" t="n"/>
@@ -20177,6 +20678,7 @@
       <c r="D339" s="11" t="n"/>
       <c r="E339" s="11" t="n"/>
       <c r="F339" s="11" t="n"/>
+      <c r="G339" s="11" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="11" t="n"/>
@@ -20184,6 +20686,7 @@
       <c r="D340" s="11" t="n"/>
       <c r="E340" s="11" t="n"/>
       <c r="F340" s="11" t="n"/>
+      <c r="G340" s="11" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="11" t="n"/>
@@ -20191,6 +20694,7 @@
       <c r="D341" s="11" t="n"/>
       <c r="E341" s="11" t="n"/>
       <c r="F341" s="11" t="n"/>
+      <c r="G341" s="11" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="11" t="n"/>
@@ -20198,6 +20702,7 @@
       <c r="D342" s="11" t="n"/>
       <c r="E342" s="11" t="n"/>
       <c r="F342" s="11" t="n"/>
+      <c r="G342" s="11" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="11" t="n"/>
@@ -20205,6 +20710,7 @@
       <c r="D343" s="11" t="n"/>
       <c r="E343" s="11" t="n"/>
       <c r="F343" s="11" t="n"/>
+      <c r="G343" s="11" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="11" t="n"/>
@@ -20212,6 +20718,7 @@
       <c r="D344" s="11" t="n"/>
       <c r="E344" s="11" t="n"/>
       <c r="F344" s="11" t="n"/>
+      <c r="G344" s="11" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="n"/>
@@ -20219,6 +20726,7 @@
       <c r="D345" s="11" t="n"/>
       <c r="E345" s="11" t="n"/>
       <c r="F345" s="11" t="n"/>
+      <c r="G345" s="11" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="11" t="n"/>
@@ -20226,6 +20734,7 @@
       <c r="D346" s="11" t="n"/>
       <c r="E346" s="11" t="n"/>
       <c r="F346" s="11" t="n"/>
+      <c r="G346" s="11" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="11" t="n"/>
@@ -20233,6 +20742,7 @@
       <c r="D347" s="11" t="n"/>
       <c r="E347" s="11" t="n"/>
       <c r="F347" s="11" t="n"/>
+      <c r="G347" s="11" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="11" t="n"/>
@@ -20240,6 +20750,7 @@
       <c r="D348" s="11" t="n"/>
       <c r="E348" s="11" t="n"/>
       <c r="F348" s="11" t="n"/>
+      <c r="G348" s="11" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="11" t="n"/>
@@ -20247,6 +20758,7 @@
       <c r="D349" s="11" t="n"/>
       <c r="E349" s="11" t="n"/>
       <c r="F349" s="11" t="n"/>
+      <c r="G349" s="11" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="11" t="n"/>
@@ -20254,6 +20766,7 @@
       <c r="D350" s="11" t="n"/>
       <c r="E350" s="11" t="n"/>
       <c r="F350" s="11" t="n"/>
+      <c r="G350" s="11" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="11" t="n"/>
@@ -20261,6 +20774,7 @@
       <c r="D351" s="11" t="n"/>
       <c r="E351" s="11" t="n"/>
       <c r="F351" s="11" t="n"/>
+      <c r="G351" s="11" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="11" t="n"/>
@@ -20268,6 +20782,7 @@
       <c r="D352" s="11" t="n"/>
       <c r="E352" s="11" t="n"/>
       <c r="F352" s="11" t="n"/>
+      <c r="G352" s="11" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="11" t="n"/>
@@ -20275,6 +20790,7 @@
       <c r="D353" s="11" t="n"/>
       <c r="E353" s="11" t="n"/>
       <c r="F353" s="11" t="n"/>
+      <c r="G353" s="11" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="11" t="n"/>
@@ -20282,6 +20798,7 @@
       <c r="D354" s="11" t="n"/>
       <c r="E354" s="11" t="n"/>
       <c r="F354" s="11" t="n"/>
+      <c r="G354" s="11" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="11" t="n"/>
@@ -20289,6 +20806,7 @@
       <c r="D355" s="11" t="n"/>
       <c r="E355" s="11" t="n"/>
       <c r="F355" s="11" t="n"/>
+      <c r="G355" s="11" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="11" t="n"/>
@@ -20296,6 +20814,7 @@
       <c r="D356" s="11" t="n"/>
       <c r="E356" s="11" t="n"/>
       <c r="F356" s="11" t="n"/>
+      <c r="G356" s="11" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="11" t="n"/>
@@ -20303,6 +20822,7 @@
       <c r="D357" s="11" t="n"/>
       <c r="E357" s="11" t="n"/>
       <c r="F357" s="11" t="n"/>
+      <c r="G357" s="11" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="11" t="n"/>
@@ -20310,6 +20830,7 @@
       <c r="D358" s="11" t="n"/>
       <c r="E358" s="11" t="n"/>
       <c r="F358" s="11" t="n"/>
+      <c r="G358" s="11" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="11" t="n"/>
@@ -20317,6 +20838,7 @@
       <c r="D359" s="11" t="n"/>
       <c r="E359" s="11" t="n"/>
       <c r="F359" s="11" t="n"/>
+      <c r="G359" s="11" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="11" t="n"/>
@@ -20324,6 +20846,7 @@
       <c r="D360" s="11" t="n"/>
       <c r="E360" s="11" t="n"/>
       <c r="F360" s="11" t="n"/>
+      <c r="G360" s="11" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="11" t="n"/>
@@ -20331,6 +20854,7 @@
       <c r="D361" s="11" t="n"/>
       <c r="E361" s="11" t="n"/>
       <c r="F361" s="11" t="n"/>
+      <c r="G361" s="11" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="11" t="n"/>
@@ -20338,6 +20862,7 @@
       <c r="D362" s="11" t="n"/>
       <c r="E362" s="11" t="n"/>
       <c r="F362" s="11" t="n"/>
+      <c r="G362" s="11" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="11" t="n"/>
@@ -20345,6 +20870,7 @@
       <c r="D363" s="11" t="n"/>
       <c r="E363" s="11" t="n"/>
       <c r="F363" s="11" t="n"/>
+      <c r="G363" s="11" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="11" t="n"/>
@@ -20352,6 +20878,7 @@
       <c r="D364" s="11" t="n"/>
       <c r="E364" s="11" t="n"/>
       <c r="F364" s="11" t="n"/>
+      <c r="G364" s="11" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="11" t="n"/>
@@ -20359,6 +20886,7 @@
       <c r="D365" s="11" t="n"/>
       <c r="E365" s="11" t="n"/>
       <c r="F365" s="11" t="n"/>
+      <c r="G365" s="11" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="11" t="n"/>
@@ -20366,6 +20894,7 @@
       <c r="D366" s="11" t="n"/>
       <c r="E366" s="11" t="n"/>
       <c r="F366" s="11" t="n"/>
+      <c r="G366" s="11" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="11" t="n"/>
@@ -20373,6 +20902,7 @@
       <c r="D367" s="11" t="n"/>
       <c r="E367" s="11" t="n"/>
       <c r="F367" s="11" t="n"/>
+      <c r="G367" s="11" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="11" t="n"/>
@@ -20380,6 +20910,7 @@
       <c r="D368" s="11" t="n"/>
       <c r="E368" s="11" t="n"/>
       <c r="F368" s="11" t="n"/>
+      <c r="G368" s="11" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="11" t="n"/>
@@ -20387,6 +20918,7 @@
       <c r="D369" s="11" t="n"/>
       <c r="E369" s="11" t="n"/>
       <c r="F369" s="11" t="n"/>
+      <c r="G369" s="11" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="11" t="n"/>
@@ -20394,6 +20926,7 @@
       <c r="D370" s="11" t="n"/>
       <c r="E370" s="11" t="n"/>
       <c r="F370" s="11" t="n"/>
+      <c r="G370" s="11" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="11" t="n"/>
@@ -20401,6 +20934,7 @@
       <c r="D371" s="11" t="n"/>
       <c r="E371" s="11" t="n"/>
       <c r="F371" s="11" t="n"/>
+      <c r="G371" s="11" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="11" t="n"/>
@@ -20408,6 +20942,7 @@
       <c r="D372" s="11" t="n"/>
       <c r="E372" s="11" t="n"/>
       <c r="F372" s="11" t="n"/>
+      <c r="G372" s="11" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="11" t="n"/>
@@ -20415,6 +20950,7 @@
       <c r="D373" s="11" t="n"/>
       <c r="E373" s="11" t="n"/>
       <c r="F373" s="11" t="n"/>
+      <c r="G373" s="11" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="11" t="n"/>
@@ -20422,6 +20958,7 @@
       <c r="D374" s="11" t="n"/>
       <c r="E374" s="11" t="n"/>
       <c r="F374" s="11" t="n"/>
+      <c r="G374" s="11" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="11" t="n"/>
@@ -20429,6 +20966,7 @@
       <c r="D375" s="11" t="n"/>
       <c r="E375" s="11" t="n"/>
       <c r="F375" s="11" t="n"/>
+      <c r="G375" s="11" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="11" t="n"/>
@@ -20436,6 +20974,7 @@
       <c r="D376" s="11" t="n"/>
       <c r="E376" s="11" t="n"/>
       <c r="F376" s="11" t="n"/>
+      <c r="G376" s="11" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="11" t="n"/>
@@ -20443,6 +20982,7 @@
       <c r="D377" s="11" t="n"/>
       <c r="E377" s="11" t="n"/>
       <c r="F377" s="11" t="n"/>
+      <c r="G377" s="11" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="11" t="n"/>
@@ -20450,6 +20990,7 @@
       <c r="D378" s="11" t="n"/>
       <c r="E378" s="11" t="n"/>
       <c r="F378" s="11" t="n"/>
+      <c r="G378" s="11" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="11" t="n"/>
@@ -20457,6 +20998,7 @@
       <c r="D379" s="11" t="n"/>
       <c r="E379" s="11" t="n"/>
       <c r="F379" s="11" t="n"/>
+      <c r="G379" s="11" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="11" t="n"/>
@@ -20464,6 +21006,7 @@
       <c r="D380" s="11" t="n"/>
       <c r="E380" s="11" t="n"/>
       <c r="F380" s="11" t="n"/>
+      <c r="G380" s="11" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="11" t="n"/>
@@ -20471,6 +21014,7 @@
       <c r="D381" s="11" t="n"/>
       <c r="E381" s="11" t="n"/>
       <c r="F381" s="11" t="n"/>
+      <c r="G381" s="11" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="11" t="n"/>
@@ -20478,6 +21022,7 @@
       <c r="D382" s="11" t="n"/>
       <c r="E382" s="11" t="n"/>
       <c r="F382" s="11" t="n"/>
+      <c r="G382" s="11" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="11" t="n"/>
@@ -20485,6 +21030,7 @@
       <c r="D383" s="11" t="n"/>
       <c r="E383" s="11" t="n"/>
       <c r="F383" s="11" t="n"/>
+      <c r="G383" s="11" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="11" t="n"/>
@@ -20492,6 +21038,7 @@
       <c r="D384" s="11" t="n"/>
       <c r="E384" s="11" t="n"/>
       <c r="F384" s="11" t="n"/>
+      <c r="G384" s="11" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="11" t="n"/>
@@ -20499,6 +21046,7 @@
       <c r="D385" s="11" t="n"/>
       <c r="E385" s="11" t="n"/>
       <c r="F385" s="11" t="n"/>
+      <c r="G385" s="11" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="11" t="n"/>
@@ -20506,6 +21054,7 @@
       <c r="D386" s="11" t="n"/>
       <c r="E386" s="11" t="n"/>
       <c r="F386" s="11" t="n"/>
+      <c r="G386" s="11" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="11" t="n"/>
@@ -20513,6 +21062,7 @@
       <c r="D387" s="11" t="n"/>
       <c r="E387" s="11" t="n"/>
       <c r="F387" s="11" t="n"/>
+      <c r="G387" s="11" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="11" t="n"/>
@@ -20520,6 +21070,7 @@
       <c r="D388" s="11" t="n"/>
       <c r="E388" s="11" t="n"/>
       <c r="F388" s="11" t="n"/>
+      <c r="G388" s="11" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="11" t="n"/>
@@ -20527,6 +21078,7 @@
       <c r="D389" s="11" t="n"/>
       <c r="E389" s="11" t="n"/>
       <c r="F389" s="11" t="n"/>
+      <c r="G389" s="11" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="11" t="n"/>
@@ -20534,6 +21086,7 @@
       <c r="D390" s="11" t="n"/>
       <c r="E390" s="11" t="n"/>
       <c r="F390" s="11" t="n"/>
+      <c r="G390" s="11" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="11" t="n"/>
@@ -20541,6 +21094,7 @@
       <c r="D391" s="11" t="n"/>
       <c r="E391" s="11" t="n"/>
       <c r="F391" s="11" t="n"/>
+      <c r="G391" s="11" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="11" t="n"/>
@@ -20548,6 +21102,7 @@
       <c r="D392" s="11" t="n"/>
       <c r="E392" s="11" t="n"/>
       <c r="F392" s="11" t="n"/>
+      <c r="G392" s="11" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="11" t="n"/>
@@ -20555,6 +21110,7 @@
       <c r="D393" s="11" t="n"/>
       <c r="E393" s="11" t="n"/>
       <c r="F393" s="11" t="n"/>
+      <c r="G393" s="11" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="11" t="n"/>
@@ -20562,6 +21118,7 @@
       <c r="D394" s="11" t="n"/>
       <c r="E394" s="11" t="n"/>
       <c r="F394" s="11" t="n"/>
+      <c r="G394" s="11" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="11" t="n"/>
@@ -20569,6 +21126,7 @@
       <c r="D395" s="11" t="n"/>
       <c r="E395" s="11" t="n"/>
       <c r="F395" s="11" t="n"/>
+      <c r="G395" s="11" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="11" t="n"/>
@@ -20576,6 +21134,7 @@
       <c r="D396" s="11" t="n"/>
       <c r="E396" s="11" t="n"/>
       <c r="F396" s="11" t="n"/>
+      <c r="G396" s="11" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="11" t="n"/>
@@ -20583,6 +21142,7 @@
       <c r="D397" s="11" t="n"/>
       <c r="E397" s="11" t="n"/>
       <c r="F397" s="11" t="n"/>
+      <c r="G397" s="11" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="11" t="n"/>
@@ -20590,6 +21150,7 @@
       <c r="D398" s="11" t="n"/>
       <c r="E398" s="11" t="n"/>
       <c r="F398" s="11" t="n"/>
+      <c r="G398" s="11" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="11" t="n"/>
@@ -20597,6 +21158,7 @@
       <c r="D399" s="11" t="n"/>
       <c r="E399" s="11" t="n"/>
       <c r="F399" s="11" t="n"/>
+      <c r="G399" s="11" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="11" t="n"/>
@@ -20604,12 +21166,16 @@
       <c r="D400" s="11" t="n"/>
       <c r="E400" s="11" t="n"/>
       <c r="F400" s="11" t="n"/>
+      <c r="G400" s="11" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$B$28:$B$37</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$B$38:$B$42</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20623,7 +21189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20631,8 +21197,9 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -20663,10 +21230,15 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>period_highlight</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>note_1</t>
         </is>
@@ -20692,10 +21264,11 @@
       <c r="E2" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -20717,10 +21290,11 @@
       <c r="E3" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -20742,10 +21316,11 @@
       <c r="E4" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -20767,10 +21342,11 @@
       <c r="E5" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -20792,10 +21368,11 @@
       <c r="E6" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -20817,10 +21394,11 @@
       <c r="E7" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -20842,10 +21420,11 @@
       <c r="E8" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -20867,10 +21446,11 @@
       <c r="E9" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -20892,10 +21472,11 @@
       <c r="E10" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -20917,10 +21498,11 @@
       <c r="E11" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -20942,10 +21524,11 @@
       <c r="E12" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -20967,10 +21550,11 @@
       <c r="E13" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -20992,10 +21576,11 @@
       <c r="E14" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -21017,10 +21602,11 @@
       <c r="E15" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -21042,10 +21628,11 @@
       <c r="E16" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -21067,10 +21654,11 @@
       <c r="E17" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -21092,10 +21680,11 @@
       <c r="E18" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -21117,10 +21706,11 @@
       <c r="E19" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -21142,10 +21732,11 @@
       <c r="E20" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -21167,10 +21758,11 @@
       <c r="E21" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -21192,10 +21784,11 @@
       <c r="E22" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -21217,10 +21810,11 @@
       <c r="E23" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -21242,10 +21836,11 @@
       <c r="E24" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -21267,10 +21862,11 @@
       <c r="E25" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -21292,10 +21888,11 @@
       <c r="E26" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -21317,10 +21914,11 @@
       <c r="E27" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -21342,10 +21940,11 @@
       <c r="E28" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -21367,10 +21966,11 @@
       <c r="E29" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -21392,10 +21992,11 @@
       <c r="E30" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -21417,10 +22018,11 @@
       <c r="E31" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -21442,10 +22044,11 @@
       <c r="E32" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -21467,10 +22070,11 @@
       <c r="E33" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -21492,10 +22096,11 @@
       <c r="E34" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -21517,10 +22122,11 @@
       <c r="E35" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -21542,10 +22148,11 @@
       <c r="E36" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -21567,10 +22174,11 @@
       <c r="E37" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -21592,10 +22200,11 @@
       <c r="E38" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -21617,10 +22226,11 @@
       <c r="E39" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -21642,10 +22252,11 @@
       <c r="E40" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -21667,10 +22278,11 @@
       <c r="E41" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -21692,10 +22304,11 @@
       <c r="E42" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -21717,10 +22330,11 @@
       <c r="E43" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -21742,10 +22356,11 @@
       <c r="E44" s="13" t="n">
         <v>46112</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -21767,10 +22382,11 @@
       <c r="E45" s="13" t="n">
         <v>46356</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -21792,10 +22408,11 @@
       <c r="E46" s="13" t="n">
         <v>46418</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -21817,10 +22434,11 @@
       <c r="E47" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -21842,10 +22460,11 @@
       <c r="E48" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -21867,10 +22486,11 @@
       <c r="E49" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -21892,10 +22512,11 @@
       <c r="E50" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -21917,10 +22538,11 @@
       <c r="E51" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -21942,10 +22564,11 @@
       <c r="E52" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -21967,10 +22590,11 @@
       <c r="E53" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -21992,10 +22616,11 @@
       <c r="E54" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -22017,10 +22642,11 @@
       <c r="E55" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -22042,10 +22668,11 @@
       <c r="E56" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -22067,10 +22694,11 @@
       <c r="E57" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F57" s="9" t="n">
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -22092,10 +22720,11 @@
       <c r="E58" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -22117,10 +22746,11 @@
       <c r="E59" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F59" s="9" t="n">
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -22142,10 +22772,11 @@
       <c r="E60" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F60" s="9" t="n">
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="9" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -22167,10 +22798,11 @@
       <c r="E61" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F61" s="9" t="n">
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -22192,10 +22824,11 @@
       <c r="E62" s="13" t="n">
         <v>46265</v>
       </c>
-      <c r="F62" s="9" t="n">
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="9" t="n"/>
+      <c r="H62" s="9" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -22217,10 +22850,11 @@
       <c r="E63" s="13" t="n">
         <v>46326</v>
       </c>
-      <c r="F63" s="9" t="n">
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="9" t="n"/>
+      <c r="H63" s="9" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -22242,10 +22876,11 @@
       <c r="E64" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F64" s="9" t="n">
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="9" t="n"/>
+      <c r="H64" s="9" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -22267,10 +22902,11 @@
       <c r="E65" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F65" s="9" t="n">
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -22292,10 +22928,11 @@
       <c r="E66" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F66" s="9" t="n">
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -22317,10 +22954,11 @@
       <c r="E67" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F67" s="9" t="n">
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -22342,10 +22980,11 @@
       <c r="E68" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F68" s="9" t="n">
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G68" s="9" t="n"/>
+      <c r="H68" s="9" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -22367,10 +23006,11 @@
       <c r="E69" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F69" s="9" t="n">
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="9" t="n"/>
+      <c r="H69" s="9" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -22392,10 +23032,11 @@
       <c r="E70" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F70" s="9" t="n">
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -22417,10 +23058,11 @@
       <c r="E71" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="F71" s="9" t="n">
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="9" t="n"/>
+      <c r="H71" s="9" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -22442,10 +23084,11 @@
       <c r="E72" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="F72" s="9" t="n">
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="9" t="n"/>
+      <c r="H72" s="9" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -22467,10 +23110,11 @@
       <c r="E73" s="13" t="n">
         <v>46387</v>
       </c>
-      <c r="F73" s="9" t="n">
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="9" t="n"/>
+      <c r="H73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -22492,10 +23136,11 @@
       <c r="E74" s="13" t="n">
         <v>46446</v>
       </c>
-      <c r="F74" s="9" t="n">
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G74" s="9" t="n"/>
+      <c r="H74" s="9" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -22517,10 +23162,11 @@
       <c r="E75" s="13" t="n">
         <v>46630</v>
       </c>
-      <c r="F75" s="9" t="n">
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="9" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -22542,10 +23188,11 @@
       <c r="E76" s="13" t="n">
         <v>46721</v>
       </c>
-      <c r="F76" s="9" t="n">
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="9" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -22567,12 +23214,18 @@
       <c r="E77" s="13" t="n">
         <v>46752</v>
       </c>
-      <c r="F77" s="9" t="n">
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="9" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$B$43:$B$47</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30084,7 +30737,7 @@
       <formula1>Lists!$B$10:$B$12</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Lists!$B$38:$B$44</formula1>
+      <formula1>Lists!$B$48:$B$54</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
